--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV12_v11_vs_strictV1_hero_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV12_v11_vs_strictV1_hero_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -535,39 +535,39 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ORP_1_3</t>
+          <t>DO_2_3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.904301320365234</v>
+        <v>4.069769486928665</v>
       </c>
       <c r="D2" t="n">
-        <v>3.852726885972241</v>
+        <v>3.954765311731117</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0515744343929927</v>
+        <v>-0.1150041751975484</v>
       </c>
       <c r="F2" t="n">
-        <v>10.28022157054415</v>
+        <v>2.981427174975562</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9612251547735419</v>
+        <v>1.058976865428478</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4235907461713913</v>
+        <v>5.897686542847834</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2932551319648094</v>
+        <v>1.971326164874552</v>
       </c>
       <c r="J2" t="n">
-        <v>0.570218312153796</v>
+        <v>0.6679700228087325</v>
       </c>
       <c r="K2" t="n">
-        <v>87.4714890843923</v>
+        <v>87.42261322906484</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -575,39 +575,39 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_1_3</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.974510897385376</v>
+        <v>4.13921756945369</v>
       </c>
       <c r="D3" t="n">
-        <v>3.923870124873021</v>
+        <v>4.114037254066393</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05064077251235455</v>
+        <v>-0.02518031538729737</v>
       </c>
       <c r="F3" t="n">
-        <v>9.058325187357445</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="G3" t="n">
-        <v>1.058976865428478</v>
+        <v>0.4235907461713913</v>
       </c>
       <c r="H3" t="n">
-        <v>1.775822743564679</v>
+        <v>0.4072987943955687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7168458781362007</v>
+        <v>0.3095470837406321</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.4398826979472141</v>
       </c>
       <c r="K3" t="n">
-        <v>86.88497882046269</v>
+        <v>95.04724666014988</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.139795847729906</v>
+        <v>4.416797068014621</v>
       </c>
       <c r="D4" t="n">
-        <v>4.11973338196626</v>
+        <v>4.405234212913766</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02006246576364568</v>
+        <v>-0.01156285510085553</v>
       </c>
       <c r="F4" t="n">
-        <v>7.363962202671879</v>
+        <v>3.877484522645813</v>
       </c>
       <c r="G4" t="n">
-        <v>1.026392961876833</v>
+        <v>0.7983056370153144</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9286412512218964</v>
+        <v>0.04887585532746823</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3421309872922776</v>
+        <v>0.1466275659824047</v>
       </c>
       <c r="J4" t="n">
         <v>0.3910068426197458</v>
       </c>
       <c r="K4" t="n">
-        <v>89.94786575431736</v>
+        <v>94.73769957640926</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -655,27 +655,27 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>DO_2_4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.146797838239641</v>
+        <v>3.912939936395083</v>
       </c>
       <c r="D5" t="n">
-        <v>4.129175636122418</v>
+        <v>3.907149817565858</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01762220211722276</v>
+        <v>-0.005790118829224866</v>
       </c>
       <c r="F5" t="n">
-        <v>4.154447702834799</v>
+        <v>1.726946888237211</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4072987943955687</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>95.43825350276963</v>
+        <v>98.27305311176279</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -695,27 +695,27 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DO_2_4</t>
+          <t>DO_1_3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.739838563292976</v>
+        <v>4.403560302427994</v>
       </c>
       <c r="D6" t="n">
-        <v>3.723850152167582</v>
+        <v>4.398000079696054</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01598841112539473</v>
+        <v>-0.005560222731940456</v>
       </c>
       <c r="F6" t="n">
-        <v>5.88139459107201</v>
+        <v>0.8634734441186055</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4887585532746823</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>93.62984685565331</v>
+        <v>99.1365265558814</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -735,39 +735,39 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORP_2_2</t>
+          <t>DO_1_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.111104729330071</v>
+        <v>4.563756091682329</v>
       </c>
       <c r="D7" t="n">
-        <v>4.10389906476872</v>
+        <v>4.563756091682329</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.007205664561350744</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.899967416096449</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7494297816878462</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04887585532746823</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1629195177582274</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3910068426197458</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>95.74780058651027</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -775,18 +775,18 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DO_1_1</t>
+          <t>DO_1_4</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.503149585034791</v>
+        <v>4.704734669401068</v>
       </c>
       <c r="D8" t="n">
-        <v>4.503149585034791</v>
+        <v>4.704734669401068</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -815,18 +815,18 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DO_1_4</t>
+          <t>DO_2_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.944725714978925</v>
+        <v>4.404947877807985</v>
       </c>
       <c r="D9" t="n">
-        <v>3.944725714978925</v>
+        <v>4.404947877807985</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -855,18 +855,18 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DO_2_1</t>
+          <t>DO_2_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.418977293521078</v>
+        <v>4.395543430045316</v>
       </c>
       <c r="D10" t="n">
-        <v>4.418977293521078</v>
+        <v>4.395543430045316</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -895,18 +895,18 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DO_2_2</t>
+          <t>ORP_1_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.485196792873761</v>
+        <v>4.104987445426761</v>
       </c>
       <c r="D11" t="n">
-        <v>4.485196792873761</v>
+        <v>4.104987445426761</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -935,18 +935,18 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORP_1_1</t>
+          <t>ORP_2_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.189182117037606</v>
+        <v>4.2660466998305</v>
       </c>
       <c r="D12" t="n">
-        <v>4.189182117037606</v>
+        <v>4.2660466998305</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -975,18 +975,18 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORP_2_1</t>
+          <t>ORP_2_3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.178407884224086</v>
+        <v>4.206544907429814</v>
       </c>
       <c r="D13" t="n">
-        <v>4.178407884224086</v>
+        <v>4.206544907429814</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1015,39 +1015,39 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORP_2_3</t>
+          <t>ORP_2_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.070327586345135</v>
+        <v>4.164774803642225</v>
       </c>
       <c r="D14" t="n">
-        <v>4.070327586345135</v>
+        <v>4.166964198546471</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.002189394904245745</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.117953730856957</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.570218312153796</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.04887585532746823</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.1629195177582274</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.3910068426197458</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>96.70902574128381</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.762078168935113</v>
+        <v>3.77875693485721</v>
       </c>
       <c r="D15" t="n">
-        <v>3.763630469902989</v>
+        <v>3.818303496684228</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001552300967876619</v>
+        <v>0.03954656182701788</v>
       </c>
       <c r="F15" t="n">
         <v>2.036493971977843</v>
@@ -1078,16 +1078,16 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="H15" t="n">
-        <v>5.848810687520365</v>
+        <v>8.031932225480611</v>
       </c>
       <c r="I15" t="n">
-        <v>1.955034213098729</v>
+        <v>1.319648093841642</v>
       </c>
       <c r="J15" t="n">
-        <v>1.221896383186706</v>
+        <v>1.01010101010101</v>
       </c>
       <c r="K15" t="n">
-        <v>88.10687520364939</v>
+        <v>86.77093515803193</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1171,19 +1171,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.94786575431736</v>
+        <v>94.73769957640926</v>
       </c>
       <c r="C3" t="n">
-        <v>7.363962202671879</v>
+        <v>3.877484522645813</v>
       </c>
       <c r="D3" t="n">
-        <v>1.026392961876833</v>
+        <v>0.7983056370153144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9286412512218964</v>
+        <v>0.04887585532746823</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3421309872922776</v>
+        <v>0.1466275659824047</v>
       </c>
       <c r="G3" t="n">
         <v>0.3910068426197458</v>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.43825350276963</v>
+        <v>99.1365265558814</v>
       </c>
       <c r="C4" t="n">
-        <v>4.154447702834799</v>
+        <v>0.8634734441186055</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4072987943955687</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1296,22 +1296,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.88497882046269</v>
+        <v>87.42261322906484</v>
       </c>
       <c r="C8" t="n">
-        <v>9.058325187357445</v>
+        <v>2.981427174975562</v>
       </c>
       <c r="D8" t="n">
         <v>1.058976865428478</v>
       </c>
       <c r="E8" t="n">
-        <v>1.775822743564679</v>
+        <v>5.897686542847834</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7168458781362007</v>
+        <v>1.971326164874552</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.6679700228087325</v>
       </c>
     </row>
     <row r="9">
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93.62984685565331</v>
+        <v>98.27305311176279</v>
       </c>
       <c r="C9" t="n">
-        <v>5.88139459107201</v>
+        <v>1.726946888237211</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4887585532746823</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88.10687520364939</v>
+        <v>86.77093515803193</v>
       </c>
       <c r="C11" t="n">
         <v>2.036493971977843</v>
@@ -1380,13 +1380,13 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="E11" t="n">
-        <v>5.848810687520365</v>
+        <v>8.031932225480611</v>
       </c>
       <c r="F11" t="n">
-        <v>1.955034213098729</v>
+        <v>1.319648093841642</v>
       </c>
       <c r="G11" t="n">
-        <v>1.221896383186706</v>
+        <v>1.01010101010101</v>
       </c>
     </row>
     <row r="12">
@@ -1396,22 +1396,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87.4714890843923</v>
+        <v>95.04724666014988</v>
       </c>
       <c r="C12" t="n">
-        <v>10.28022157054415</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9612251547735419</v>
+        <v>0.4235907461713913</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4235907461713913</v>
+        <v>0.4072987943955687</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2932551319648094</v>
+        <v>0.3095470837406321</v>
       </c>
       <c r="G12" t="n">
-        <v>0.570218312153796</v>
+        <v>0.4398826979472141</v>
       </c>
     </row>
     <row r="13">
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>95.74780058651027</v>
+        <v>96.70902574128381</v>
       </c>
       <c r="C14" t="n">
-        <v>2.899967416096449</v>
+        <v>2.117953730856957</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7494297816878462</v>
+        <v>0.570218312153796</v>
       </c>
       <c r="E14" t="n">
         <v>0.04887585532746823</v>
@@ -1525,10 +1525,10 @@
         <v>45870</v>
       </c>
       <c r="B2" t="n">
-        <v>4.516066807302172</v>
+        <v>4.550806778696802</v>
       </c>
       <c r="C2" t="n">
-        <v>4.516066807302172</v>
+        <v>4.550806778696802</v>
       </c>
     </row>
     <row r="3">
@@ -1536,10 +1536,10 @@
         <v>45871</v>
       </c>
       <c r="B3" t="n">
-        <v>4.481525304483302</v>
+        <v>4.491290992217966</v>
       </c>
       <c r="C3" t="n">
-        <v>4.481525304483302</v>
+        <v>4.491290992217966</v>
       </c>
     </row>
     <row r="4">
@@ -1547,10 +1547,10 @@
         <v>45872</v>
       </c>
       <c r="B4" t="n">
-        <v>4.408260938141019</v>
+        <v>4.478801406810811</v>
       </c>
       <c r="C4" t="n">
-        <v>4.408260938141019</v>
+        <v>4.478801406810811</v>
       </c>
     </row>
     <row r="5">
@@ -1558,10 +1558,10 @@
         <v>45873</v>
       </c>
       <c r="B5" t="n">
-        <v>4.14221016599859</v>
+        <v>4.317005211744529</v>
       </c>
       <c r="C5" t="n">
-        <v>4.14221016599859</v>
+        <v>4.317005211744529</v>
       </c>
     </row>
     <row r="6">
@@ -1569,10 +1569,10 @@
         <v>45874</v>
       </c>
       <c r="B6" t="n">
-        <v>4.23463456252022</v>
+        <v>4.379578623018772</v>
       </c>
       <c r="C6" t="n">
-        <v>4.23463456252022</v>
+        <v>4.379578623018772</v>
       </c>
     </row>
     <row r="7">
@@ -1580,10 +1580,10 @@
         <v>45875</v>
       </c>
       <c r="B7" t="n">
-        <v>4.198301502922329</v>
+        <v>4.408090474787095</v>
       </c>
       <c r="C7" t="n">
-        <v>4.198301502922329</v>
+        <v>4.408090474787095</v>
       </c>
     </row>
     <row r="8">
@@ -1591,10 +1591,10 @@
         <v>45876</v>
       </c>
       <c r="B8" t="n">
-        <v>4.278468011544575</v>
+        <v>4.521859838767156</v>
       </c>
       <c r="C8" t="n">
-        <v>4.278468011544575</v>
+        <v>4.521859838767156</v>
       </c>
     </row>
     <row r="9">
@@ -1602,10 +1602,10 @@
         <v>45877</v>
       </c>
       <c r="B9" t="n">
-        <v>4.36594162520783</v>
+        <v>4.504864798038458</v>
       </c>
       <c r="C9" t="n">
-        <v>4.341627493738557</v>
+        <v>4.504864798038458</v>
       </c>
     </row>
     <row r="10">
@@ -1613,10 +1613,10 @@
         <v>45878</v>
       </c>
       <c r="B10" t="n">
-        <v>4.251519860163958</v>
+        <v>4.480590462045601</v>
       </c>
       <c r="C10" t="n">
-        <v>4.251519860163958</v>
+        <v>4.480590462045601</v>
       </c>
     </row>
     <row r="11">
@@ -1624,10 +1624,10 @@
         <v>45879</v>
       </c>
       <c r="B11" t="n">
-        <v>4.196583961829451</v>
+        <v>4.402031425226692</v>
       </c>
       <c r="C11" t="n">
-        <v>4.196583961829451</v>
+        <v>4.402031425226692</v>
       </c>
     </row>
     <row r="12">
@@ -1635,10 +1635,10 @@
         <v>45880</v>
       </c>
       <c r="B12" t="n">
-        <v>4.30954305214731</v>
+        <v>4.499279912871334</v>
       </c>
       <c r="C12" t="n">
-        <v>4.30954305214731</v>
+        <v>4.499279912871334</v>
       </c>
     </row>
     <row r="13">
@@ -1646,10 +1646,10 @@
         <v>45881</v>
       </c>
       <c r="B13" t="n">
-        <v>4.32239346432914</v>
+        <v>4.495914263102534</v>
       </c>
       <c r="C13" t="n">
-        <v>4.32239346432914</v>
+        <v>4.495914263102534</v>
       </c>
     </row>
     <row r="14">
@@ -1657,10 +1657,10 @@
         <v>45882</v>
       </c>
       <c r="B14" t="n">
-        <v>4.24175616737176</v>
+        <v>4.470124946665625</v>
       </c>
       <c r="C14" t="n">
-        <v>4.24175616737176</v>
+        <v>4.470124946665625</v>
       </c>
     </row>
     <row r="15">
@@ -1668,10 +1668,10 @@
         <v>45883</v>
       </c>
       <c r="B15" t="n">
-        <v>4.31840733577745</v>
+        <v>4.505430730505763</v>
       </c>
       <c r="C15" t="n">
-        <v>4.31840733577745</v>
+        <v>4.505430730505763</v>
       </c>
     </row>
     <row r="16">
@@ -1679,10 +1679,10 @@
         <v>45884</v>
       </c>
       <c r="B16" t="n">
-        <v>4.364802867666292</v>
+        <v>4.492115535657659</v>
       </c>
       <c r="C16" t="n">
-        <v>4.364802867666292</v>
+        <v>4.492115535657659</v>
       </c>
     </row>
     <row r="17">
@@ -1690,10 +1690,10 @@
         <v>45885</v>
       </c>
       <c r="B17" t="n">
-        <v>4.333869723662281</v>
+        <v>4.471558351779957</v>
       </c>
       <c r="C17" t="n">
-        <v>4.310191845325095</v>
+        <v>4.471558351779957</v>
       </c>
     </row>
     <row r="18">
@@ -1701,10 +1701,10 @@
         <v>45886</v>
       </c>
       <c r="B18" t="n">
-        <v>4.302450030229158</v>
+        <v>4.478621750513256</v>
       </c>
       <c r="C18" t="n">
-        <v>4.302450030229158</v>
+        <v>4.478621750513256</v>
       </c>
     </row>
     <row r="19">
@@ -1712,10 +1712,10 @@
         <v>45887</v>
       </c>
       <c r="B19" t="n">
-        <v>4.281909126034705</v>
+        <v>4.473724944645149</v>
       </c>
       <c r="C19" t="n">
-        <v>4.281909126034705</v>
+        <v>4.473724944645149</v>
       </c>
     </row>
     <row r="20">
@@ -1723,10 +1723,10 @@
         <v>45888</v>
       </c>
       <c r="B20" t="n">
-        <v>4.352354104378264</v>
+        <v>4.458945033964708</v>
       </c>
       <c r="C20" t="n">
-        <v>4.352354104378264</v>
+        <v>4.458945033964708</v>
       </c>
     </row>
     <row r="21">
@@ -1734,10 +1734,10 @@
         <v>45889</v>
       </c>
       <c r="B21" t="n">
-        <v>4.355455216133316</v>
+        <v>4.4612431098102</v>
       </c>
       <c r="C21" t="n">
-        <v>4.355455216133316</v>
+        <v>4.4612431098102</v>
       </c>
     </row>
     <row r="22">
@@ -1745,10 +1745,10 @@
         <v>45890</v>
       </c>
       <c r="B22" t="n">
-        <v>4.363354355390397</v>
+        <v>4.445562082826374</v>
       </c>
       <c r="C22" t="n">
-        <v>4.363354355390397</v>
+        <v>4.445562082826374</v>
       </c>
     </row>
     <row r="23">
@@ -1756,10 +1756,10 @@
         <v>45891</v>
       </c>
       <c r="B23" t="n">
-        <v>4.37301523583371</v>
+        <v>4.465829857443206</v>
       </c>
       <c r="C23" t="n">
-        <v>4.37301523583371</v>
+        <v>4.465829857443206</v>
       </c>
     </row>
     <row r="24">
@@ -1767,10 +1767,10 @@
         <v>45892</v>
       </c>
       <c r="B24" t="n">
-        <v>4.299626620581825</v>
+        <v>4.459156774747385</v>
       </c>
       <c r="C24" t="n">
-        <v>4.299626620581825</v>
+        <v>4.459156774747385</v>
       </c>
     </row>
     <row r="25">
@@ -1778,10 +1778,10 @@
         <v>45893</v>
       </c>
       <c r="B25" t="n">
-        <v>4.345679140050939</v>
+        <v>4.44627033293506</v>
       </c>
       <c r="C25" t="n">
-        <v>4.345679140050939</v>
+        <v>4.44627033293506</v>
       </c>
     </row>
     <row r="26">
@@ -1789,10 +1789,10 @@
         <v>45894</v>
       </c>
       <c r="B26" t="n">
-        <v>4.375557135239745</v>
+        <v>4.453616463275117</v>
       </c>
       <c r="C26" t="n">
-        <v>4.375557135239745</v>
+        <v>4.453616463275117</v>
       </c>
     </row>
     <row r="27">
@@ -1800,10 +1800,10 @@
         <v>45895</v>
       </c>
       <c r="B27" t="n">
-        <v>4.341264628702061</v>
+        <v>4.452755920096219</v>
       </c>
       <c r="C27" t="n">
-        <v>4.341264628702061</v>
+        <v>4.452755920096219</v>
       </c>
     </row>
     <row r="28">
@@ -1811,10 +1811,10 @@
         <v>45896</v>
       </c>
       <c r="B28" t="n">
-        <v>4.322609649500153</v>
+        <v>4.454567572073698</v>
       </c>
       <c r="C28" t="n">
-        <v>4.322609649500153</v>
+        <v>4.454567572073698</v>
       </c>
     </row>
     <row r="29">
@@ -1822,10 +1822,10 @@
         <v>45897</v>
       </c>
       <c r="B29" t="n">
-        <v>4.332592918849314</v>
+        <v>4.440863485213735</v>
       </c>
       <c r="C29" t="n">
-        <v>4.332592918849314</v>
+        <v>4.440863485213735</v>
       </c>
     </row>
     <row r="30">
@@ -1833,10 +1833,10 @@
         <v>45898</v>
       </c>
       <c r="B30" t="n">
-        <v>4.3934414291616</v>
+        <v>4.491093458222737</v>
       </c>
       <c r="C30" t="n">
-        <v>4.3934414291616</v>
+        <v>4.491093458222737</v>
       </c>
     </row>
     <row r="31">
@@ -1844,10 +1844,10 @@
         <v>45899</v>
       </c>
       <c r="B31" t="n">
-        <v>4.346483781586511</v>
+        <v>4.4768385905326</v>
       </c>
       <c r="C31" t="n">
-        <v>4.346483781586511</v>
+        <v>4.4768385905326</v>
       </c>
     </row>
     <row r="32">
@@ -1855,10 +1855,10 @@
         <v>45900</v>
       </c>
       <c r="B32" t="n">
-        <v>4.343108432405083</v>
+        <v>4.495079578100452</v>
       </c>
       <c r="C32" t="n">
-        <v>4.343108432405083</v>
+        <v>4.495079578100452</v>
       </c>
     </row>
     <row r="33">
@@ -1866,10 +1866,10 @@
         <v>45901</v>
       </c>
       <c r="B33" t="n">
-        <v>4.356232879011899</v>
+        <v>4.468259184064085</v>
       </c>
       <c r="C33" t="n">
-        <v>4.356232879011899</v>
+        <v>4.468259184064085</v>
       </c>
     </row>
     <row r="34">
@@ -1877,10 +1877,10 @@
         <v>45902</v>
       </c>
       <c r="B34" t="n">
-        <v>4.403370969268328</v>
+        <v>4.517355360006881</v>
       </c>
       <c r="C34" t="n">
-        <v>4.403370969268328</v>
+        <v>4.517355360006881</v>
       </c>
     </row>
     <row r="35">
@@ -1888,10 +1888,10 @@
         <v>45903</v>
       </c>
       <c r="B35" t="n">
-        <v>4.363109023933339</v>
+        <v>4.441979492270363</v>
       </c>
       <c r="C35" t="n">
-        <v>4.363109023933339</v>
+        <v>4.441979492270363</v>
       </c>
     </row>
     <row r="36">
@@ -1899,10 +1899,10 @@
         <v>45904</v>
       </c>
       <c r="B36" t="n">
-        <v>4.292887592322134</v>
+        <v>4.448732558537577</v>
       </c>
       <c r="C36" t="n">
-        <v>4.292887592322134</v>
+        <v>4.448732558537577</v>
       </c>
     </row>
     <row r="37">
@@ -1910,10 +1910,10 @@
         <v>45905</v>
       </c>
       <c r="B37" t="n">
-        <v>4.301204221106167</v>
+        <v>4.453720267231112</v>
       </c>
       <c r="C37" t="n">
-        <v>4.301204221106167</v>
+        <v>4.453720267231112</v>
       </c>
     </row>
     <row r="38">
@@ -1921,10 +1921,10 @@
         <v>45906</v>
       </c>
       <c r="B38" t="n">
-        <v>4.284071566149587</v>
+        <v>4.440563440187846</v>
       </c>
       <c r="C38" t="n">
-        <v>4.284071566149587</v>
+        <v>4.440563440187846</v>
       </c>
     </row>
     <row r="39">
@@ -1932,10 +1932,10 @@
         <v>45907</v>
       </c>
       <c r="B39" t="n">
-        <v>4.321998223949785</v>
+        <v>4.4228126715486</v>
       </c>
       <c r="C39" t="n">
-        <v>4.321998223949785</v>
+        <v>4.4228126715486</v>
       </c>
     </row>
     <row r="40">
@@ -1943,10 +1943,10 @@
         <v>45908</v>
       </c>
       <c r="B40" t="n">
-        <v>4.246437748961733</v>
+        <v>4.416545834477949</v>
       </c>
       <c r="C40" t="n">
-        <v>4.246437748961733</v>
+        <v>4.416545834477949</v>
       </c>
     </row>
     <row r="41">
@@ -1954,10 +1954,10 @@
         <v>45909</v>
       </c>
       <c r="B41" t="n">
-        <v>4.238457641371961</v>
+        <v>4.354577133937146</v>
       </c>
       <c r="C41" t="n">
-        <v>4.238457641371961</v>
+        <v>4.354577133937146</v>
       </c>
     </row>
     <row r="42">
@@ -1965,10 +1965,10 @@
         <v>45910</v>
       </c>
       <c r="B42" t="n">
-        <v>4.269373233608048</v>
+        <v>4.376783826263686</v>
       </c>
       <c r="C42" t="n">
-        <v>4.269373233608048</v>
+        <v>4.376783826263686</v>
       </c>
     </row>
     <row r="43">
@@ -1976,10 +1976,10 @@
         <v>45911</v>
       </c>
       <c r="B43" t="n">
-        <v>4.297568523379487</v>
+        <v>4.404722964950011</v>
       </c>
       <c r="C43" t="n">
-        <v>4.297568523379487</v>
+        <v>4.404722964950011</v>
       </c>
     </row>
     <row r="44">
@@ -1987,10 +1987,10 @@
         <v>45912</v>
       </c>
       <c r="B44" t="n">
-        <v>3.988043382738267</v>
+        <v>4.198253575896558</v>
       </c>
       <c r="C44" t="n">
-        <v>3.988043382738267</v>
+        <v>4.198253575896558</v>
       </c>
     </row>
     <row r="45">
@@ -1998,10 +1998,10 @@
         <v>45913</v>
       </c>
       <c r="B45" t="n">
-        <v>4.084007178321574</v>
+        <v>4.34166844998484</v>
       </c>
       <c r="C45" t="n">
-        <v>4.084007178321574</v>
+        <v>4.34166844998484</v>
       </c>
     </row>
     <row r="46">
@@ -2009,10 +2009,10 @@
         <v>45914</v>
       </c>
       <c r="B46" t="n">
-        <v>4.167576929524007</v>
+        <v>4.383477809075909</v>
       </c>
       <c r="C46" t="n">
-        <v>4.118762285458632</v>
+        <v>4.344876137002511</v>
       </c>
     </row>
     <row r="47">
@@ -2020,10 +2020,10 @@
         <v>45915</v>
       </c>
       <c r="B47" t="n">
-        <v>4.251136009345595</v>
+        <v>4.358607989178887</v>
       </c>
       <c r="C47" t="n">
-        <v>4.185216690018339</v>
+        <v>4.358607989178887</v>
       </c>
     </row>
     <row r="48">
@@ -2031,10 +2031,10 @@
         <v>45916</v>
       </c>
       <c r="B48" t="n">
-        <v>4.292709589777118</v>
+        <v>4.414200419818424</v>
       </c>
       <c r="C48" t="n">
-        <v>4.292709589777118</v>
+        <v>4.414200419818424</v>
       </c>
     </row>
     <row r="49">
@@ -2042,10 +2042,10 @@
         <v>45917</v>
       </c>
       <c r="B49" t="n">
-        <v>4.16479420072872</v>
+        <v>4.246423975112271</v>
       </c>
       <c r="C49" t="n">
-        <v>4.16479420072872</v>
+        <v>4.246423975112271</v>
       </c>
     </row>
     <row r="50">
@@ -2053,10 +2053,10 @@
         <v>45918</v>
       </c>
       <c r="B50" t="n">
-        <v>4.247741676276371</v>
+        <v>4.345928957272575</v>
       </c>
       <c r="C50" t="n">
-        <v>4.247741676276371</v>
+        <v>4.345928957272575</v>
       </c>
     </row>
     <row r="51">
@@ -2064,10 +2064,10 @@
         <v>45919</v>
       </c>
       <c r="B51" t="n">
-        <v>4.187652994746271</v>
+        <v>4.298312644451833</v>
       </c>
       <c r="C51" t="n">
-        <v>4.187652994746271</v>
+        <v>4.298312644451833</v>
       </c>
     </row>
     <row r="52">
@@ -2075,10 +2075,10 @@
         <v>45920</v>
       </c>
       <c r="B52" t="n">
-        <v>4.156957200393238</v>
+        <v>4.339837008503503</v>
       </c>
       <c r="C52" t="n">
-        <v>4.156957200393238</v>
+        <v>4.339837008503503</v>
       </c>
     </row>
     <row r="53">
@@ -2086,10 +2086,10 @@
         <v>45921</v>
       </c>
       <c r="B53" t="n">
-        <v>4.098048199468096</v>
+        <v>4.298194568479151</v>
       </c>
       <c r="C53" t="n">
-        <v>4.098048199468096</v>
+        <v>4.298194568479151</v>
       </c>
     </row>
     <row r="54">
@@ -2097,10 +2097,10 @@
         <v>45922</v>
       </c>
       <c r="B54" t="n">
-        <v>4.281951432985645</v>
+        <v>4.400945317956134</v>
       </c>
       <c r="C54" t="n">
-        <v>4.281951432985645</v>
+        <v>4.400945317956134</v>
       </c>
     </row>
     <row r="55">
@@ -2108,10 +2108,10 @@
         <v>45923</v>
       </c>
       <c r="B55" t="n">
-        <v>4.249117423193853</v>
+        <v>4.384278685633879</v>
       </c>
       <c r="C55" t="n">
-        <v>4.249117423193853</v>
+        <v>4.384278685633879</v>
       </c>
     </row>
     <row r="56">
@@ -2119,10 +2119,10 @@
         <v>45924</v>
       </c>
       <c r="B56" t="n">
-        <v>4.322887825562726</v>
+        <v>4.459938451852521</v>
       </c>
       <c r="C56" t="n">
-        <v>4.240051094078114</v>
+        <v>4.459938451852521</v>
       </c>
     </row>
     <row r="57">
@@ -2130,10 +2130,10 @@
         <v>45925</v>
       </c>
       <c r="B57" t="n">
-        <v>4.213730906747678</v>
+        <v>4.475814430074523</v>
       </c>
       <c r="C57" t="n">
-        <v>4.174355771065002</v>
+        <v>4.475814430074523</v>
       </c>
     </row>
     <row r="58">
@@ -2141,10 +2141,10 @@
         <v>45926</v>
       </c>
       <c r="B58" t="n">
-        <v>4.288063784877349</v>
+        <v>4.4153639453885</v>
       </c>
       <c r="C58" t="n">
-        <v>4.275736942336795</v>
+        <v>4.401914439146316</v>
       </c>
     </row>
     <row r="59">
@@ -2152,10 +2152,10 @@
         <v>45927</v>
       </c>
       <c r="B59" t="n">
-        <v>4.329652815354487</v>
+        <v>4.352558908007262</v>
       </c>
       <c r="C59" t="n">
-        <v>4.329652815354487</v>
+        <v>4.352558908007262</v>
       </c>
     </row>
     <row r="60">
@@ -2163,10 +2163,10 @@
         <v>45928</v>
       </c>
       <c r="B60" t="n">
-        <v>4.259638373565461</v>
+        <v>4.392820960362134</v>
       </c>
       <c r="C60" t="n">
-        <v>4.259638373565461</v>
+        <v>4.379739220757669</v>
       </c>
     </row>
     <row r="61">
@@ -2174,10 +2174,10 @@
         <v>45929</v>
       </c>
       <c r="B61" t="n">
-        <v>4.346846224760661</v>
+        <v>4.454506917572321</v>
       </c>
       <c r="C61" t="n">
-        <v>4.346846224760661</v>
+        <v>4.454506917572321</v>
       </c>
     </row>
     <row r="62">
@@ -2185,10 +2185,10 @@
         <v>45930</v>
       </c>
       <c r="B62" t="n">
-        <v>4.352127881089393</v>
+        <v>4.439437297264005</v>
       </c>
       <c r="C62" t="n">
-        <v>4.320583481201361</v>
+        <v>4.434637533578824</v>
       </c>
     </row>
     <row r="63">
@@ -2196,10 +2196,10 @@
         <v>45931</v>
       </c>
       <c r="B63" t="n">
-        <v>4.383285674163956</v>
+        <v>4.448622727169796</v>
       </c>
       <c r="C63" t="n">
-        <v>4.320948396984425</v>
+        <v>4.44711206922393</v>
       </c>
     </row>
     <row r="64">
@@ -2207,10 +2207,10 @@
         <v>45932</v>
       </c>
       <c r="B64" t="n">
-        <v>4.156858277897717</v>
+        <v>4.331400503599296</v>
       </c>
       <c r="C64" t="n">
-        <v>4.156858277897717</v>
+        <v>4.331400503599296</v>
       </c>
     </row>
     <row r="65">
@@ -2218,10 +2218,10 @@
         <v>45933</v>
       </c>
       <c r="B65" t="n">
-        <v>4.323029669858787</v>
+        <v>4.419826621292529</v>
       </c>
       <c r="C65" t="n">
-        <v>4.323029669858787</v>
+        <v>4.41129927757114</v>
       </c>
     </row>
     <row r="66">
@@ -2229,10 +2229,10 @@
         <v>45934</v>
       </c>
       <c r="B66" t="n">
-        <v>4.117610056829553</v>
+        <v>4.411897126231835</v>
       </c>
       <c r="C66" t="n">
-        <v>4.090205210437583</v>
+        <v>4.411897126231835</v>
       </c>
     </row>
     <row r="67">
@@ -2240,10 +2240,10 @@
         <v>45935</v>
       </c>
       <c r="B67" t="n">
-        <v>4.228154384298005</v>
+        <v>4.424628732516729</v>
       </c>
       <c r="C67" t="n">
-        <v>4.205258324131206</v>
+        <v>4.404616520615223</v>
       </c>
     </row>
     <row r="68">
@@ -2251,10 +2251,10 @@
         <v>45936</v>
       </c>
       <c r="B68" t="n">
-        <v>4.228966601771406</v>
+        <v>4.448154833696002</v>
       </c>
       <c r="C68" t="n">
-        <v>4.205276809769559</v>
+        <v>4.40788505865124</v>
       </c>
     </row>
     <row r="69">
@@ -2262,10 +2262,10 @@
         <v>45937</v>
       </c>
       <c r="B69" t="n">
-        <v>4.285075893834691</v>
+        <v>4.407356505126775</v>
       </c>
       <c r="C69" t="n">
-        <v>4.285075893834691</v>
+        <v>4.39580005022544</v>
       </c>
     </row>
     <row r="70">
@@ -2273,10 +2273,10 @@
         <v>45938</v>
       </c>
       <c r="B70" t="n">
-        <v>4.381168068879036</v>
+        <v>4.419838501395427</v>
       </c>
       <c r="C70" t="n">
-        <v>4.361169487908514</v>
+        <v>4.412776657713051</v>
       </c>
     </row>
     <row r="71">
@@ -2284,10 +2284,10 @@
         <v>45939</v>
       </c>
       <c r="B71" t="n">
-        <v>4.316023873371185</v>
+        <v>4.460460167174654</v>
       </c>
       <c r="C71" t="n">
-        <v>4.328048804104415</v>
+        <v>4.460460167174654</v>
       </c>
     </row>
     <row r="72">
@@ -2295,10 +2295,10 @@
         <v>45940</v>
       </c>
       <c r="B72" t="n">
-        <v>4.35750972465761</v>
+        <v>4.44222285870516</v>
       </c>
       <c r="C72" t="n">
-        <v>4.35750972465761</v>
+        <v>4.473475484947253</v>
       </c>
     </row>
     <row r="73">
@@ -2306,10 +2306,10 @@
         <v>45941</v>
       </c>
       <c r="B73" t="n">
-        <v>4.278343767359104</v>
+        <v>4.435109828881709</v>
       </c>
       <c r="C73" t="n">
-        <v>4.278343767359104</v>
+        <v>4.435109828881709</v>
       </c>
     </row>
     <row r="74">
@@ -2317,10 +2317,10 @@
         <v>45942</v>
       </c>
       <c r="B74" t="n">
-        <v>4.386132052680097</v>
+        <v>4.431580415001976</v>
       </c>
       <c r="C74" t="n">
-        <v>4.386132052680097</v>
+        <v>4.431580415001976</v>
       </c>
     </row>
     <row r="75">
@@ -2328,10 +2328,10 @@
         <v>45943</v>
       </c>
       <c r="B75" t="n">
-        <v>4.296904613190527</v>
+        <v>4.412115492623244</v>
       </c>
       <c r="C75" t="n">
-        <v>4.296904613190527</v>
+        <v>4.412115492623244</v>
       </c>
     </row>
     <row r="76">
@@ -2339,10 +2339,10 @@
         <v>45944</v>
       </c>
       <c r="B76" t="n">
-        <v>4.328248612254535</v>
+        <v>4.412622953155796</v>
       </c>
       <c r="C76" t="n">
-        <v>4.328248612254535</v>
+        <v>4.412622953155796</v>
       </c>
     </row>
     <row r="77">
@@ -2350,10 +2350,10 @@
         <v>45945</v>
       </c>
       <c r="B77" t="n">
-        <v>4.171862064647913</v>
+        <v>4.404266812625424</v>
       </c>
       <c r="C77" t="n">
-        <v>4.171862064647913</v>
+        <v>4.404266812625424</v>
       </c>
     </row>
     <row r="78">
@@ -2361,10 +2361,10 @@
         <v>45946</v>
       </c>
       <c r="B78" t="n">
-        <v>4.237290104426604</v>
+        <v>4.436592401656824</v>
       </c>
       <c r="C78" t="n">
-        <v>4.237290104426604</v>
+        <v>4.436592401656824</v>
       </c>
     </row>
     <row r="79">
@@ -2372,10 +2372,10 @@
         <v>45947</v>
       </c>
       <c r="B79" t="n">
-        <v>4.29443120893969</v>
+        <v>4.424039006715997</v>
       </c>
       <c r="C79" t="n">
-        <v>4.29443120893969</v>
+        <v>4.424039006715997</v>
       </c>
     </row>
     <row r="80">
@@ -2383,10 +2383,10 @@
         <v>45948</v>
       </c>
       <c r="B80" t="n">
-        <v>4.352890681652729</v>
+        <v>4.44765694234237</v>
       </c>
       <c r="C80" t="n">
-        <v>4.352890681652729</v>
+        <v>4.44765694234237</v>
       </c>
     </row>
     <row r="81">
@@ -2394,10 +2394,10 @@
         <v>45949</v>
       </c>
       <c r="B81" t="n">
-        <v>4.241592947296487</v>
+        <v>4.364353309544963</v>
       </c>
       <c r="C81" t="n">
-        <v>4.241592947296487</v>
+        <v>4.364353309544963</v>
       </c>
     </row>
     <row r="82">
@@ -2405,10 +2405,10 @@
         <v>45950</v>
       </c>
       <c r="B82" t="n">
-        <v>4.150276290287011</v>
+        <v>4.383965965080968</v>
       </c>
       <c r="C82" t="n">
-        <v>4.150276290287011</v>
+        <v>4.383965965080968</v>
       </c>
     </row>
     <row r="83">
@@ -2416,10 +2416,10 @@
         <v>45951</v>
       </c>
       <c r="B83" t="n">
-        <v>4.207587531044033</v>
+        <v>4.286448795107429</v>
       </c>
       <c r="C83" t="n">
-        <v>4.127638598217258</v>
+        <v>4.286448795107429</v>
       </c>
     </row>
     <row r="84">
@@ -2427,10 +2427,10 @@
         <v>45952</v>
       </c>
       <c r="B84" t="n">
-        <v>4.101385862490108</v>
+        <v>4.111746096141168</v>
       </c>
       <c r="C84" t="n">
-        <v>3.996395204050965</v>
+        <v>4.111746096141168</v>
       </c>
     </row>
     <row r="85">
@@ -2438,10 +2438,10 @@
         <v>45953</v>
       </c>
       <c r="B85" t="n">
-        <v>4.106798451492225</v>
+        <v>4.279615739044174</v>
       </c>
       <c r="C85" t="n">
-        <v>4.106798451492225</v>
+        <v>4.279615739044174</v>
       </c>
     </row>
     <row r="86">
@@ -2449,10 +2449,10 @@
         <v>45954</v>
       </c>
       <c r="B86" t="n">
-        <v>4.14916099381001</v>
+        <v>4.358758496746858</v>
       </c>
       <c r="C86" t="n">
-        <v>4.14916099381001</v>
+        <v>4.358758496746858</v>
       </c>
     </row>
     <row r="87">
@@ -2460,10 +2460,10 @@
         <v>45955</v>
       </c>
       <c r="B87" t="n">
-        <v>4.115805127167187</v>
+        <v>4.351268419973931</v>
       </c>
       <c r="C87" t="n">
-        <v>4.115805127167187</v>
+        <v>4.351268419973931</v>
       </c>
     </row>
     <row r="88">
@@ -2471,10 +2471,10 @@
         <v>45956</v>
       </c>
       <c r="B88" t="n">
-        <v>4.181402595188156</v>
+        <v>4.416673184471487</v>
       </c>
       <c r="C88" t="n">
-        <v>4.181402595188156</v>
+        <v>4.416673184471487</v>
       </c>
     </row>
     <row r="89">
@@ -2482,10 +2482,10 @@
         <v>45957</v>
       </c>
       <c r="B89" t="n">
-        <v>4.310963294641562</v>
+        <v>4.396581619579717</v>
       </c>
       <c r="C89" t="n">
-        <v>4.310963294641562</v>
+        <v>4.396581619579717</v>
       </c>
     </row>
     <row r="90">
@@ -2493,10 +2493,10 @@
         <v>45958</v>
       </c>
       <c r="B90" t="n">
-        <v>4.199168166453654</v>
+        <v>4.284868802327406</v>
       </c>
       <c r="C90" t="n">
-        <v>4.199168166453654</v>
+        <v>4.284868802327406</v>
       </c>
     </row>
     <row r="91">
@@ -2504,10 +2504,10 @@
         <v>45959</v>
       </c>
       <c r="B91" t="n">
-        <v>4.316706616190415</v>
+        <v>4.330977789092275</v>
       </c>
       <c r="C91" t="n">
-        <v>4.316706616190415</v>
+        <v>4.330977789092275</v>
       </c>
     </row>
     <row r="92">
@@ -2515,10 +2515,10 @@
         <v>45960</v>
       </c>
       <c r="B92" t="n">
-        <v>4.317667720099004</v>
+        <v>4.424484700849487</v>
       </c>
       <c r="C92" t="n">
-        <v>4.31446726453461</v>
+        <v>4.417859865119986</v>
       </c>
     </row>
     <row r="93">
@@ -2526,10 +2526,10 @@
         <v>45961</v>
       </c>
       <c r="B93" t="n">
-        <v>4.232782751463569</v>
+        <v>4.381765006724674</v>
       </c>
       <c r="C93" t="n">
-        <v>4.225349487757557</v>
+        <v>4.381765006724674</v>
       </c>
     </row>
     <row r="94">
@@ -2537,10 +2537,10 @@
         <v>45962</v>
       </c>
       <c r="B94" t="n">
-        <v>4.255285730745689</v>
+        <v>4.431240771847746</v>
       </c>
       <c r="C94" t="n">
-        <v>4.255285730745689</v>
+        <v>4.431240771847746</v>
       </c>
     </row>
     <row r="95">
@@ -2548,10 +2548,10 @@
         <v>45963</v>
       </c>
       <c r="B95" t="n">
-        <v>4.324633936463705</v>
+        <v>4.400752841431887</v>
       </c>
       <c r="C95" t="n">
-        <v>4.324633936463705</v>
+        <v>4.400752841431887</v>
       </c>
     </row>
     <row r="96">
@@ -2559,10 +2559,10 @@
         <v>45964</v>
       </c>
       <c r="B96" t="n">
-        <v>4.219909312556424</v>
+        <v>4.393748259562787</v>
       </c>
       <c r="C96" t="n">
-        <v>4.219909312556424</v>
+        <v>4.393748259562787</v>
       </c>
     </row>
     <row r="97">
@@ -2570,10 +2570,10 @@
         <v>45965</v>
       </c>
       <c r="B97" t="n">
-        <v>4.290252052122113</v>
+        <v>4.394733357413747</v>
       </c>
       <c r="C97" t="n">
-        <v>4.290252052122113</v>
+        <v>4.394733357413747</v>
       </c>
     </row>
     <row r="98">
@@ -2581,10 +2581,10 @@
         <v>45966</v>
       </c>
       <c r="B98" t="n">
-        <v>4.20501725858483</v>
+        <v>4.315380230731188</v>
       </c>
       <c r="C98" t="n">
-        <v>4.20501725858483</v>
+        <v>4.315380230731188</v>
       </c>
     </row>
     <row r="99">
@@ -2592,10 +2592,10 @@
         <v>45967</v>
       </c>
       <c r="B99" t="n">
-        <v>4.174246938017395</v>
+        <v>4.305837462677302</v>
       </c>
       <c r="C99" t="n">
-        <v>4.174246938017395</v>
+        <v>4.305837462677302</v>
       </c>
     </row>
     <row r="100">
@@ -2603,10 +2603,10 @@
         <v>45968</v>
       </c>
       <c r="B100" t="n">
-        <v>4.229075725424819</v>
+        <v>4.400112639687075</v>
       </c>
       <c r="C100" t="n">
-        <v>4.229075725424819</v>
+        <v>4.400112639687075</v>
       </c>
     </row>
     <row r="101">
@@ -2614,10 +2614,10 @@
         <v>45969</v>
       </c>
       <c r="B101" t="n">
-        <v>4.237808070543277</v>
+        <v>4.419568650164198</v>
       </c>
       <c r="C101" t="n">
-        <v>4.228290247514376</v>
+        <v>4.419568650164198</v>
       </c>
     </row>
     <row r="102">
@@ -2625,10 +2625,10 @@
         <v>45970</v>
       </c>
       <c r="B102" t="n">
-        <v>4.283754024615165</v>
+        <v>4.418988767064426</v>
       </c>
       <c r="C102" t="n">
-        <v>4.313150796790632</v>
+        <v>4.418988767064426</v>
       </c>
     </row>
     <row r="103">
@@ -2636,10 +2636,10 @@
         <v>45971</v>
       </c>
       <c r="B103" t="n">
-        <v>4.196201209790677</v>
+        <v>4.387757198485907</v>
       </c>
       <c r="C103" t="n">
-        <v>4.196201209790677</v>
+        <v>4.387757198485907</v>
       </c>
     </row>
     <row r="104">
@@ -2647,10 +2647,10 @@
         <v>45972</v>
       </c>
       <c r="B104" t="n">
-        <v>4.176382305033563</v>
+        <v>4.373676454870157</v>
       </c>
       <c r="C104" t="n">
-        <v>4.176382305033563</v>
+        <v>4.373676454870157</v>
       </c>
     </row>
     <row r="105">
@@ -2658,10 +2658,10 @@
         <v>45973</v>
       </c>
       <c r="B105" t="n">
-        <v>4.207316308325288</v>
+        <v>4.323720021249467</v>
       </c>
       <c r="C105" t="n">
-        <v>4.207316308325288</v>
+        <v>4.332217008913166</v>
       </c>
     </row>
     <row r="106">
@@ -2669,10 +2669,10 @@
         <v>45974</v>
       </c>
       <c r="B106" t="n">
-        <v>4.089265798927105</v>
+        <v>4.351127614559865</v>
       </c>
       <c r="C106" t="n">
-        <v>4.089265798927105</v>
+        <v>4.351127614559865</v>
       </c>
     </row>
     <row r="107">
@@ -2680,10 +2680,10 @@
         <v>45975</v>
       </c>
       <c r="B107" t="n">
-        <v>4.203948565889055</v>
+        <v>4.421287175520365</v>
       </c>
       <c r="C107" t="n">
-        <v>4.203948565889055</v>
+        <v>4.418938666339739</v>
       </c>
     </row>
     <row r="108">
@@ -2691,10 +2691,10 @@
         <v>45976</v>
       </c>
       <c r="B108" t="n">
-        <v>4.204630197580643</v>
+        <v>4.359909627016278</v>
       </c>
       <c r="C108" t="n">
-        <v>4.16743231789665</v>
+        <v>4.359909627016278</v>
       </c>
     </row>
     <row r="109">
@@ -2702,10 +2702,10 @@
         <v>45977</v>
       </c>
       <c r="B109" t="n">
-        <v>4.143543301782127</v>
+        <v>4.302470923911287</v>
       </c>
       <c r="C109" t="n">
-        <v>4.143543301782127</v>
+        <v>4.302470923911287</v>
       </c>
     </row>
     <row r="110">
@@ -2713,10 +2713,10 @@
         <v>45978</v>
       </c>
       <c r="B110" t="n">
-        <v>4.290814965522425</v>
+        <v>4.391665214686874</v>
       </c>
       <c r="C110" t="n">
-        <v>4.290814965522425</v>
+        <v>4.391665214686874</v>
       </c>
     </row>
     <row r="111">
@@ -2724,10 +2724,10 @@
         <v>45979</v>
       </c>
       <c r="B111" t="n">
-        <v>4.289702649068974</v>
+        <v>4.366161457758413</v>
       </c>
       <c r="C111" t="n">
-        <v>4.289702649068974</v>
+        <v>4.366161457758413</v>
       </c>
     </row>
     <row r="112">
@@ -2735,10 +2735,10 @@
         <v>45980</v>
       </c>
       <c r="B112" t="n">
-        <v>4.256169058041078</v>
+        <v>4.393666891184649</v>
       </c>
       <c r="C112" t="n">
-        <v>4.256169058041078</v>
+        <v>4.393666891184649</v>
       </c>
     </row>
     <row r="113">
@@ -2746,10 +2746,10 @@
         <v>45981</v>
       </c>
       <c r="B113" t="n">
-        <v>4.289868913549695</v>
+        <v>4.407342848129148</v>
       </c>
       <c r="C113" t="n">
-        <v>4.283689380524311</v>
+        <v>4.407342848129148</v>
       </c>
     </row>
     <row r="114">
@@ -2757,10 +2757,10 @@
         <v>45982</v>
       </c>
       <c r="B114" t="n">
-        <v>4.271967396287208</v>
+        <v>4.347562753757702</v>
       </c>
       <c r="C114" t="n">
-        <v>4.271967396287208</v>
+        <v>4.347562753757702</v>
       </c>
     </row>
     <row r="115">
@@ -2768,10 +2768,10 @@
         <v>45983</v>
       </c>
       <c r="B115" t="n">
-        <v>4.199605783735806</v>
+        <v>4.407953126029099</v>
       </c>
       <c r="C115" t="n">
-        <v>4.199605783735806</v>
+        <v>4.407953126029099</v>
       </c>
     </row>
     <row r="116">
@@ -2779,10 +2779,10 @@
         <v>45984</v>
       </c>
       <c r="B116" t="n">
-        <v>4.131696976704202</v>
+        <v>4.389205395447081</v>
       </c>
       <c r="C116" t="n">
-        <v>4.131696976704202</v>
+        <v>4.389205395447081</v>
       </c>
     </row>
     <row r="117">
@@ -2790,10 +2790,10 @@
         <v>45985</v>
       </c>
       <c r="B117" t="n">
-        <v>4.17469985124323</v>
+        <v>4.370053551988651</v>
       </c>
       <c r="C117" t="n">
-        <v>4.17469985124323</v>
+        <v>4.370053551988651</v>
       </c>
     </row>
     <row r="118">
@@ -2801,10 +2801,10 @@
         <v>45986</v>
       </c>
       <c r="B118" t="n">
-        <v>4.102755858767557</v>
+        <v>4.391650884448048</v>
       </c>
       <c r="C118" t="n">
-        <v>4.102755858767557</v>
+        <v>4.391650884448048</v>
       </c>
     </row>
     <row r="119">
@@ -2812,10 +2812,10 @@
         <v>45987</v>
       </c>
       <c r="B119" t="n">
-        <v>4.308811733056757</v>
+        <v>4.441566147016368</v>
       </c>
       <c r="C119" t="n">
-        <v>4.301803072195089</v>
+        <v>4.441566147016368</v>
       </c>
     </row>
     <row r="120">
@@ -2823,10 +2823,10 @@
         <v>45988</v>
       </c>
       <c r="B120" t="n">
-        <v>4.246612016044972</v>
+        <v>4.412811588110653</v>
       </c>
       <c r="C120" t="n">
-        <v>4.246612016044972</v>
+        <v>4.412811588110653</v>
       </c>
     </row>
     <row r="121">
@@ -2834,10 +2834,10 @@
         <v>45989</v>
       </c>
       <c r="B121" t="n">
-        <v>4.336847269499939</v>
+        <v>4.400215104506776</v>
       </c>
       <c r="C121" t="n">
-        <v>4.336847269499939</v>
+        <v>4.400215104506776</v>
       </c>
     </row>
     <row r="122">
@@ -2845,10 +2845,10 @@
         <v>45990</v>
       </c>
       <c r="B122" t="n">
-        <v>4.282316591806554</v>
+        <v>4.416637825459072</v>
       </c>
       <c r="C122" t="n">
-        <v>4.282316591806554</v>
+        <v>4.416637825459072</v>
       </c>
     </row>
     <row r="123">
@@ -2856,10 +2856,10 @@
         <v>45991</v>
       </c>
       <c r="B123" t="n">
-        <v>4.220422677052909</v>
+        <v>4.427200099431129</v>
       </c>
       <c r="C123" t="n">
-        <v>4.220422677052909</v>
+        <v>4.427200099431129</v>
       </c>
     </row>
     <row r="124">
@@ -2867,10 +2867,10 @@
         <v>45992</v>
       </c>
       <c r="B124" t="n">
-        <v>4.289389751626062</v>
+        <v>4.415339025117182</v>
       </c>
       <c r="C124" t="n">
-        <v>4.289389751626062</v>
+        <v>4.415339025117182</v>
       </c>
     </row>
     <row r="125">
@@ -2878,10 +2878,10 @@
         <v>45993</v>
       </c>
       <c r="B125" t="n">
-        <v>4.286082004934235</v>
+        <v>4.399526876257063</v>
       </c>
       <c r="C125" t="n">
-        <v>4.282532539417232</v>
+        <v>4.399526876257063</v>
       </c>
     </row>
     <row r="126">
@@ -2889,10 +2889,10 @@
         <v>45994</v>
       </c>
       <c r="B126" t="n">
-        <v>4.187531888480065</v>
+        <v>4.440130229458708</v>
       </c>
       <c r="C126" t="n">
-        <v>4.187531888480065</v>
+        <v>4.440130229458708</v>
       </c>
     </row>
     <row r="127">
@@ -2900,10 +2900,10 @@
         <v>45995</v>
       </c>
       <c r="B127" t="n">
-        <v>4.2837419590831</v>
+        <v>4.445743247105971</v>
       </c>
       <c r="C127" t="n">
-        <v>4.2837419590831</v>
+        <v>4.445743247105971</v>
       </c>
     </row>
     <row r="128">
@@ -2911,10 +2911,10 @@
         <v>45996</v>
       </c>
       <c r="B128" t="n">
-        <v>4.304523697673131</v>
+        <v>4.45742695979172</v>
       </c>
       <c r="C128" t="n">
-        <v>4.304523697673131</v>
+        <v>4.45742695979172</v>
       </c>
     </row>
     <row r="129">
@@ -2922,10 +2922,10 @@
         <v>45997</v>
       </c>
       <c r="B129" t="n">
-        <v>4.318710858097282</v>
+        <v>4.386279414514373</v>
       </c>
       <c r="C129" t="n">
-        <v>4.294153012947478</v>
+        <v>4.386279414514373</v>
       </c>
     </row>
     <row r="130">
@@ -2933,10 +2933,10 @@
         <v>45998</v>
       </c>
       <c r="B130" t="n">
-        <v>4.21582407806881</v>
+        <v>4.377672404126907</v>
       </c>
       <c r="C130" t="n">
-        <v>4.21582407806881</v>
+        <v>4.377672404126907</v>
       </c>
     </row>
     <row r="131">
@@ -2944,10 +2944,10 @@
         <v>45999</v>
       </c>
       <c r="B131" t="n">
-        <v>4.198477279103104</v>
+        <v>4.421655500489181</v>
       </c>
       <c r="C131" t="n">
-        <v>4.198477279103104</v>
+        <v>4.421655500489181</v>
       </c>
     </row>
     <row r="132">
@@ -2955,10 +2955,10 @@
         <v>46000</v>
       </c>
       <c r="B132" t="n">
-        <v>4.312231687406355</v>
+        <v>4.371408492503349</v>
       </c>
       <c r="C132" t="n">
-        <v>4.312231687406355</v>
+        <v>4.371408492503349</v>
       </c>
     </row>
     <row r="133">
@@ -2966,10 +2966,10 @@
         <v>46001</v>
       </c>
       <c r="B133" t="n">
-        <v>4.365182311786134</v>
+        <v>4.437624156121888</v>
       </c>
       <c r="C133" t="n">
-        <v>4.312110011029587</v>
+        <v>4.437624156121888</v>
       </c>
     </row>
     <row r="134">
@@ -2977,10 +2977,10 @@
         <v>46002</v>
       </c>
       <c r="B134" t="n">
-        <v>4.257171651661103</v>
+        <v>4.423868613887422</v>
       </c>
       <c r="C134" t="n">
-        <v>4.257171651661103</v>
+        <v>4.423868613887422</v>
       </c>
     </row>
     <row r="135">
@@ -2988,10 +2988,10 @@
         <v>46003</v>
       </c>
       <c r="B135" t="n">
-        <v>4.266029675399853</v>
+        <v>4.400263111814354</v>
       </c>
       <c r="C135" t="n">
-        <v>4.266029675399853</v>
+        <v>4.400263111814354</v>
       </c>
     </row>
     <row r="136">
@@ -2999,10 +2999,10 @@
         <v>46004</v>
       </c>
       <c r="B136" t="n">
-        <v>4.326289455623007</v>
+        <v>4.430095532909537</v>
       </c>
       <c r="C136" t="n">
-        <v>4.326289455623007</v>
+        <v>4.430095532909537</v>
       </c>
     </row>
     <row r="137">
@@ -3010,10 +3010,10 @@
         <v>46005</v>
       </c>
       <c r="B137" t="n">
-        <v>4.283796165542202</v>
+        <v>4.425398494745943</v>
       </c>
       <c r="C137" t="n">
-        <v>4.283796165542202</v>
+        <v>4.425398494745943</v>
       </c>
     </row>
     <row r="138">
@@ -3021,10 +3021,10 @@
         <v>46006</v>
       </c>
       <c r="B138" t="n">
-        <v>4.315455628684502</v>
+        <v>4.447118310508857</v>
       </c>
       <c r="C138" t="n">
-        <v>4.315455628684502</v>
+        <v>4.447118310508857</v>
       </c>
     </row>
     <row r="139">
@@ -3032,10 +3032,10 @@
         <v>46007</v>
       </c>
       <c r="B139" t="n">
-        <v>4.238636238947808</v>
+        <v>4.435260925256493</v>
       </c>
       <c r="C139" t="n">
-        <v>4.238636238947808</v>
+        <v>4.435260925256493</v>
       </c>
     </row>
     <row r="140">
@@ -3043,10 +3043,10 @@
         <v>46008</v>
       </c>
       <c r="B140" t="n">
-        <v>4.270579834599252</v>
+        <v>4.397449118175375</v>
       </c>
       <c r="C140" t="n">
-        <v>4.270579834599252</v>
+        <v>4.397449118175375</v>
       </c>
     </row>
     <row r="141">
@@ -3054,10 +3054,10 @@
         <v>46009</v>
       </c>
       <c r="B141" t="n">
-        <v>4.20720879698249</v>
+        <v>4.384528244036699</v>
       </c>
       <c r="C141" t="n">
-        <v>4.20720879698249</v>
+        <v>4.384528244036699</v>
       </c>
     </row>
     <row r="142">
@@ -3065,10 +3065,10 @@
         <v>46010</v>
       </c>
       <c r="B142" t="n">
-        <v>4.269130556701883</v>
+        <v>4.380250349324729</v>
       </c>
       <c r="C142" t="n">
-        <v>4.269130556701883</v>
+        <v>4.380250349324729</v>
       </c>
     </row>
     <row r="143">
@@ -3076,10 +3076,10 @@
         <v>46011</v>
       </c>
       <c r="B143" t="n">
-        <v>4.154390699088196</v>
+        <v>4.381190211396083</v>
       </c>
       <c r="C143" t="n">
-        <v>4.154390699088196</v>
+        <v>4.381190211396083</v>
       </c>
     </row>
     <row r="144">
@@ -3087,10 +3087,10 @@
         <v>46012</v>
       </c>
       <c r="B144" t="n">
-        <v>3.99589183495293</v>
+        <v>4.300276395491455</v>
       </c>
       <c r="C144" t="n">
-        <v>3.99589183495293</v>
+        <v>4.300276395491455</v>
       </c>
     </row>
     <row r="145">
@@ -3098,10 +3098,10 @@
         <v>46013</v>
       </c>
       <c r="B145" t="n">
-        <v>4.143635557149361</v>
+        <v>4.25621480209975</v>
       </c>
       <c r="C145" t="n">
-        <v>4.143635557149361</v>
+        <v>4.25621480209975</v>
       </c>
     </row>
     <row r="146">
@@ -3109,10 +3109,10 @@
         <v>46014</v>
       </c>
       <c r="B146" t="n">
-        <v>4.085723009883087</v>
+        <v>4.316835394533486</v>
       </c>
       <c r="C146" t="n">
-        <v>4.085723009883087</v>
+        <v>4.316835394533486</v>
       </c>
     </row>
     <row r="147">
@@ -3120,10 +3120,10 @@
         <v>46015</v>
       </c>
       <c r="B147" t="n">
-        <v>3.791825051649205</v>
+        <v>4.151843266478377</v>
       </c>
       <c r="C147" t="n">
-        <v>3.791825051649205</v>
+        <v>4.151843266478377</v>
       </c>
     </row>
     <row r="148">
@@ -3131,10 +3131,10 @@
         <v>46016</v>
       </c>
       <c r="B148" t="n">
-        <v>4.005305271246323</v>
+        <v>4.263137362539621</v>
       </c>
       <c r="C148" t="n">
-        <v>4.005305271246323</v>
+        <v>4.263137362539621</v>
       </c>
     </row>
     <row r="149">
@@ -3142,10 +3142,10 @@
         <v>46017</v>
       </c>
       <c r="B149" t="n">
-        <v>4.042878112620974</v>
+        <v>4.299888866716721</v>
       </c>
       <c r="C149" t="n">
-        <v>3.960466584421544</v>
+        <v>4.150357082514819</v>
       </c>
     </row>
     <row r="150">
@@ -3153,10 +3153,10 @@
         <v>46018</v>
       </c>
       <c r="B150" t="n">
-        <v>3.960903765818351</v>
+        <v>4.281891123016315</v>
       </c>
       <c r="C150" t="n">
-        <v>3.960903765818351</v>
+        <v>4.235692863154348</v>
       </c>
     </row>
     <row r="151">
@@ -3164,10 +3164,10 @@
         <v>46019</v>
       </c>
       <c r="B151" t="n">
-        <v>4.194562231427263</v>
+        <v>4.375385012024429</v>
       </c>
       <c r="C151" t="n">
-        <v>4.194562231427263</v>
+        <v>4.375385012024429</v>
       </c>
     </row>
     <row r="152">
@@ -3175,10 +3175,10 @@
         <v>46020</v>
       </c>
       <c r="B152" t="n">
-        <v>4.093538425388352</v>
+        <v>4.228014431199322</v>
       </c>
       <c r="C152" t="n">
-        <v>4.093538425388352</v>
+        <v>4.228014431199322</v>
       </c>
     </row>
     <row r="153">
@@ -3186,10 +3186,10 @@
         <v>46021</v>
       </c>
       <c r="B153" t="n">
-        <v>4.165665134419716</v>
+        <v>4.385414852310701</v>
       </c>
       <c r="C153" t="n">
-        <v>4.165665134419716</v>
+        <v>4.385414852310701</v>
       </c>
     </row>
     <row r="154">
@@ -3197,10 +3197,10 @@
         <v>46022</v>
       </c>
       <c r="B154" t="n">
-        <v>4.134789635019077</v>
+        <v>4.406241073719764</v>
       </c>
       <c r="C154" t="n">
-        <v>4.134789635019077</v>
+        <v>4.406241073719764</v>
       </c>
     </row>
     <row r="155">
@@ -3208,10 +3208,10 @@
         <v>46023</v>
       </c>
       <c r="B155" t="n">
-        <v>4.154174651213959</v>
+        <v>4.374413980625778</v>
       </c>
       <c r="C155" t="n">
-        <v>4.154174651213959</v>
+        <v>4.374413980625778</v>
       </c>
     </row>
     <row r="156">
@@ -3219,10 +3219,10 @@
         <v>46024</v>
       </c>
       <c r="B156" t="n">
-        <v>4.227534628610974</v>
+        <v>4.366378711307195</v>
       </c>
       <c r="C156" t="n">
-        <v>4.227534628610974</v>
+        <v>4.366378711307195</v>
       </c>
     </row>
     <row r="157">
@@ -3230,10 +3230,10 @@
         <v>46025</v>
       </c>
       <c r="B157" t="n">
-        <v>4.306799467621295</v>
+        <v>4.391522597901255</v>
       </c>
       <c r="C157" t="n">
-        <v>4.306799467621295</v>
+        <v>4.391522597901255</v>
       </c>
     </row>
     <row r="158">
@@ -3241,10 +3241,10 @@
         <v>46026</v>
       </c>
       <c r="B158" t="n">
-        <v>4.189203869473692</v>
+        <v>4.357389952257252</v>
       </c>
       <c r="C158" t="n">
-        <v>4.189203869473692</v>
+        <v>4.357389952257252</v>
       </c>
     </row>
     <row r="159">
@@ -3252,10 +3252,10 @@
         <v>46027</v>
       </c>
       <c r="B159" t="n">
-        <v>4.252329785947408</v>
+        <v>4.355127084002206</v>
       </c>
       <c r="C159" t="n">
-        <v>4.252329785947408</v>
+        <v>4.355127084002206</v>
       </c>
     </row>
     <row r="160">
@@ -3263,10 +3263,10 @@
         <v>46028</v>
       </c>
       <c r="B160" t="n">
-        <v>4.050308905716884</v>
+        <v>4.330953468374436</v>
       </c>
       <c r="C160" t="n">
-        <v>4.050308905716884</v>
+        <v>4.330953468374436</v>
       </c>
     </row>
     <row r="161">
@@ -3274,10 +3274,10 @@
         <v>46029</v>
       </c>
       <c r="B161" t="n">
-        <v>3.891671849683281</v>
+        <v>4.100896576794787</v>
       </c>
       <c r="C161" t="n">
-        <v>3.895775210051536</v>
+        <v>4.100896576794787</v>
       </c>
     </row>
     <row r="162">
@@ -3285,10 +3285,10 @@
         <v>46030</v>
       </c>
       <c r="B162" t="n">
-        <v>4.021990706873958</v>
+        <v>4.273777296447053</v>
       </c>
       <c r="C162" t="n">
-        <v>4.021990706873958</v>
+        <v>4.226239761443557</v>
       </c>
     </row>
     <row r="163">
@@ -3296,10 +3296,10 @@
         <v>46031</v>
       </c>
       <c r="B163" t="n">
-        <v>3.874177661466397</v>
+        <v>4.324648287432504</v>
       </c>
       <c r="C163" t="n">
-        <v>3.874177661466397</v>
+        <v>4.324648287432504</v>
       </c>
     </row>
     <row r="164">
@@ -3307,10 +3307,10 @@
         <v>46032</v>
       </c>
       <c r="B164" t="n">
-        <v>4.243513074617458</v>
+        <v>4.455314738873971</v>
       </c>
       <c r="C164" t="n">
-        <v>4.243513074617458</v>
+        <v>4.455314738873971</v>
       </c>
     </row>
     <row r="165">
@@ -3318,10 +3318,10 @@
         <v>46033</v>
       </c>
       <c r="B165" t="n">
-        <v>4.046314300887831</v>
+        <v>4.259171467943776</v>
       </c>
       <c r="C165" t="n">
-        <v>4.046314300887831</v>
+        <v>4.259171467943776</v>
       </c>
     </row>
     <row r="166">
@@ -3329,10 +3329,10 @@
         <v>46034</v>
       </c>
       <c r="B166" t="n">
-        <v>4.212535185911481</v>
+        <v>4.359794516602141</v>
       </c>
       <c r="C166" t="n">
-        <v>4.212535185911481</v>
+        <v>4.359794516602141</v>
       </c>
     </row>
     <row r="167">
@@ -3340,10 +3340,10 @@
         <v>46035</v>
       </c>
       <c r="B167" t="n">
-        <v>4.198556601247214</v>
+        <v>4.455547950778575</v>
       </c>
       <c r="C167" t="n">
-        <v>4.198556601247214</v>
+        <v>4.455547950778575</v>
       </c>
     </row>
     <row r="168">
@@ -3351,10 +3351,10 @@
         <v>46036</v>
       </c>
       <c r="B168" t="n">
-        <v>4.028800292514291</v>
+        <v>4.317829825441179</v>
       </c>
       <c r="C168" t="n">
-        <v>4.028800292514291</v>
+        <v>4.317829825441179</v>
       </c>
     </row>
     <row r="169">
@@ -3362,10 +3362,10 @@
         <v>46037</v>
       </c>
       <c r="B169" t="n">
-        <v>4.199154975877136</v>
+        <v>4.400262810169881</v>
       </c>
       <c r="C169" t="n">
-        <v>4.199154975877136</v>
+        <v>4.400262810169881</v>
       </c>
     </row>
     <row r="170">
@@ -3373,10 +3373,10 @@
         <v>46038</v>
       </c>
       <c r="B170" t="n">
-        <v>4.131119206478685</v>
+        <v>4.384392300754966</v>
       </c>
       <c r="C170" t="n">
-        <v>4.131119206478685</v>
+        <v>4.384392300754966</v>
       </c>
     </row>
     <row r="171">
@@ -3384,10 +3384,10 @@
         <v>46039</v>
       </c>
       <c r="B171" t="n">
-        <v>4.146695553517937</v>
+        <v>4.377346261759214</v>
       </c>
       <c r="C171" t="n">
-        <v>4.146695553517937</v>
+        <v>4.377346261759214</v>
       </c>
     </row>
     <row r="172">
@@ -3395,10 +3395,10 @@
         <v>46040</v>
       </c>
       <c r="B172" t="n">
-        <v>4.112739378052337</v>
+        <v>4.345903577734251</v>
       </c>
       <c r="C172" t="n">
-        <v>4.11262990971054</v>
+        <v>4.345903577734251</v>
       </c>
     </row>
     <row r="173">
@@ -3406,10 +3406,10 @@
         <v>46041</v>
       </c>
       <c r="B173" t="n">
-        <v>4.221306197423146</v>
+        <v>4.403132371356339</v>
       </c>
       <c r="C173" t="n">
-        <v>4.221306197423146</v>
+        <v>4.403132371356339</v>
       </c>
     </row>
     <row r="174">
@@ -3417,10 +3417,10 @@
         <v>46042</v>
       </c>
       <c r="B174" t="n">
-        <v>4.291974639137205</v>
+        <v>4.441663477672707</v>
       </c>
       <c r="C174" t="n">
-        <v>4.291974639137205</v>
+        <v>4.441663477672707</v>
       </c>
     </row>
     <row r="175">
@@ -3428,10 +3428,10 @@
         <v>46043</v>
       </c>
       <c r="B175" t="n">
-        <v>4.26873961418395</v>
+        <v>4.418783551765717</v>
       </c>
       <c r="C175" t="n">
-        <v>4.26873961418395</v>
+        <v>4.418783551765717</v>
       </c>
     </row>
     <row r="176">
@@ -3439,10 +3439,10 @@
         <v>46044</v>
       </c>
       <c r="B176" t="n">
-        <v>4.272871058762355</v>
+        <v>4.43025234065078</v>
       </c>
       <c r="C176" t="n">
-        <v>4.272871058762355</v>
+        <v>4.43025234065078</v>
       </c>
     </row>
     <row r="177">
@@ -3450,10 +3450,10 @@
         <v>46045</v>
       </c>
       <c r="B177" t="n">
-        <v>4.18493844813196</v>
+        <v>4.389639480014468</v>
       </c>
       <c r="C177" t="n">
-        <v>4.18493844813196</v>
+        <v>4.389639480014468</v>
       </c>
     </row>
     <row r="178">
@@ -3461,10 +3461,10 @@
         <v>46046</v>
       </c>
       <c r="B178" t="n">
-        <v>4.284357515305958</v>
+        <v>4.351823722641601</v>
       </c>
       <c r="C178" t="n">
-        <v>4.284357515305958</v>
+        <v>4.351823722641601</v>
       </c>
     </row>
     <row r="179">
@@ -3472,10 +3472,10 @@
         <v>46047</v>
       </c>
       <c r="B179" t="n">
-        <v>4.289813557831612</v>
+        <v>4.357651869164293</v>
       </c>
       <c r="C179" t="n">
-        <v>4.289813557831612</v>
+        <v>4.357651869164293</v>
       </c>
     </row>
     <row r="180">
@@ -3483,10 +3483,10 @@
         <v>46048</v>
       </c>
       <c r="B180" t="n">
-        <v>4.263947367935951</v>
+        <v>4.425819404482612</v>
       </c>
       <c r="C180" t="n">
-        <v>4.263947367935951</v>
+        <v>4.425819404482612</v>
       </c>
     </row>
     <row r="181">
@@ -3494,10 +3494,10 @@
         <v>46049</v>
       </c>
       <c r="B181" t="n">
-        <v>4.278575127375627</v>
+        <v>4.412329808020745</v>
       </c>
       <c r="C181" t="n">
-        <v>4.278575127375627</v>
+        <v>4.412329808020745</v>
       </c>
     </row>
     <row r="182">
@@ -3505,10 +3505,10 @@
         <v>46050</v>
       </c>
       <c r="B182" t="n">
-        <v>4.216756601315666</v>
+        <v>4.503030605914658</v>
       </c>
       <c r="C182" t="n">
-        <v>4.216756601315666</v>
+        <v>4.503030605914658</v>
       </c>
     </row>
     <row r="183">
@@ -3516,10 +3516,10 @@
         <v>46051</v>
       </c>
       <c r="B183" t="n">
-        <v>4.294888634139643</v>
+        <v>4.463376565544276</v>
       </c>
       <c r="C183" t="n">
-        <v>4.294888634139643</v>
+        <v>4.463376565544276</v>
       </c>
     </row>
     <row r="184">
@@ -3527,10 +3527,10 @@
         <v>46052</v>
       </c>
       <c r="B184" t="n">
-        <v>4.155430110752564</v>
+        <v>4.387408534405907</v>
       </c>
       <c r="C184" t="n">
-        <v>4.155430110752564</v>
+        <v>4.387408534405907</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>46053</v>
       </c>
       <c r="B185" t="n">
-        <v>4.318586225575003</v>
+        <v>4.3927856891838</v>
       </c>
       <c r="C185" t="n">
-        <v>4.318586225575003</v>
+        <v>4.3927856891838</v>
       </c>
     </row>
     <row r="186">
@@ -3549,10 +3549,10 @@
         <v>46054</v>
       </c>
       <c r="B186" t="n">
-        <v>4.344572000905822</v>
+        <v>4.407881582776237</v>
       </c>
       <c r="C186" t="n">
-        <v>4.344572000905822</v>
+        <v>4.407881582776237</v>
       </c>
     </row>
     <row r="187">
@@ -3560,10 +3560,10 @@
         <v>46055</v>
       </c>
       <c r="B187" t="n">
-        <v>4.305600853360099</v>
+        <v>4.360765488477806</v>
       </c>
       <c r="C187" t="n">
-        <v>4.305600853360099</v>
+        <v>4.360765488477806</v>
       </c>
     </row>
     <row r="188">
@@ -3571,10 +3571,10 @@
         <v>46056</v>
       </c>
       <c r="B188" t="n">
-        <v>4.239083171416739</v>
+        <v>4.407068342919383</v>
       </c>
       <c r="C188" t="n">
-        <v>4.239083171416739</v>
+        <v>4.407068342919383</v>
       </c>
     </row>
     <row r="189">
@@ -3582,10 +3582,10 @@
         <v>46057</v>
       </c>
       <c r="B189" t="n">
-        <v>4.158988027773804</v>
+        <v>4.416027121059203</v>
       </c>
       <c r="C189" t="n">
-        <v>4.158988027773804</v>
+        <v>4.416027121059203</v>
       </c>
     </row>
     <row r="190">
@@ -3593,10 +3593,10 @@
         <v>46058</v>
       </c>
       <c r="B190" t="n">
-        <v>4.252146703370813</v>
+        <v>4.429256216930807</v>
       </c>
       <c r="C190" t="n">
-        <v>4.252146703370813</v>
+        <v>4.429256216930807</v>
       </c>
     </row>
     <row r="191">
@@ -3604,10 +3604,10 @@
         <v>46059</v>
       </c>
       <c r="B191" t="n">
-        <v>4.27388061625379</v>
+        <v>4.418337290791038</v>
       </c>
       <c r="C191" t="n">
-        <v>4.27388061625379</v>
+        <v>4.418337290791038</v>
       </c>
     </row>
     <row r="192">
@@ -3615,10 +3615,10 @@
         <v>46060</v>
       </c>
       <c r="B192" t="n">
-        <v>4.33623220470467</v>
+        <v>4.461912518586617</v>
       </c>
       <c r="C192" t="n">
-        <v>4.33623220470467</v>
+        <v>4.461912518586617</v>
       </c>
     </row>
     <row r="193">
@@ -3626,10 +3626,10 @@
         <v>46061</v>
       </c>
       <c r="B193" t="n">
-        <v>4.275619798657031</v>
+        <v>4.44954161267889</v>
       </c>
       <c r="C193" t="n">
-        <v>4.275619798657031</v>
+        <v>4.44954161267889</v>
       </c>
     </row>
     <row r="194">
@@ -3637,10 +3637,10 @@
         <v>46062</v>
       </c>
       <c r="B194" t="n">
-        <v>4.26008202072291</v>
+        <v>4.405201361250505</v>
       </c>
       <c r="C194" t="n">
-        <v>4.26008202072291</v>
+        <v>4.405201361250505</v>
       </c>
     </row>
     <row r="195">
@@ -3648,10 +3648,10 @@
         <v>46063</v>
       </c>
       <c r="B195" t="n">
-        <v>4.203923525688587</v>
+        <v>4.407812052943402</v>
       </c>
       <c r="C195" t="n">
-        <v>4.203923525688587</v>
+        <v>4.407812052943402</v>
       </c>
     </row>
     <row r="196">
@@ -3659,10 +3659,10 @@
         <v>46064</v>
       </c>
       <c r="B196" t="n">
-        <v>4.241519763166549</v>
+        <v>4.318713146388808</v>
       </c>
       <c r="C196" t="n">
-        <v>4.241519763166549</v>
+        <v>4.318713146388808</v>
       </c>
     </row>
     <row r="197">
@@ -3670,10 +3670,10 @@
         <v>46065</v>
       </c>
       <c r="B197" t="n">
-        <v>4.161392309247239</v>
+        <v>4.360335563679131</v>
       </c>
       <c r="C197" t="n">
-        <v>4.161392309247239</v>
+        <v>4.360335563679131</v>
       </c>
     </row>
     <row r="198">
@@ -3681,10 +3681,10 @@
         <v>46066</v>
       </c>
       <c r="B198" t="n">
-        <v>4.087954008804109</v>
+        <v>4.331568962043228</v>
       </c>
       <c r="C198" t="n">
-        <v>4.087954008804109</v>
+        <v>4.331568962043228</v>
       </c>
     </row>
     <row r="199">
@@ -3692,10 +3692,10 @@
         <v>46067</v>
       </c>
       <c r="B199" t="n">
-        <v>4.124388429355546</v>
+        <v>4.333393243748395</v>
       </c>
       <c r="C199" t="n">
-        <v>4.031114965470016</v>
+        <v>4.333393243748395</v>
       </c>
     </row>
     <row r="200">
@@ -3703,10 +3703,10 @@
         <v>46068</v>
       </c>
       <c r="B200" t="n">
-        <v>3.833103242477095</v>
+        <v>4.164426795639802</v>
       </c>
       <c r="C200" t="n">
-        <v>3.833103242477095</v>
+        <v>4.164426795639802</v>
       </c>
     </row>
     <row r="201">
@@ -3714,10 +3714,10 @@
         <v>46069</v>
       </c>
       <c r="B201" t="n">
-        <v>3.941696617404612</v>
+        <v>4.045688322063411</v>
       </c>
       <c r="C201" t="n">
-        <v>3.941696617404612</v>
+        <v>3.99872986954666</v>
       </c>
     </row>
     <row r="202">
@@ -3725,10 +3725,10 @@
         <v>46070</v>
       </c>
       <c r="B202" t="n">
-        <v>3.90043867996715</v>
+        <v>4.146441616281752</v>
       </c>
       <c r="C202" t="n">
-        <v>3.90043867996715</v>
+        <v>4.146441616281752</v>
       </c>
     </row>
     <row r="203">
@@ -3736,10 +3736,10 @@
         <v>46071</v>
       </c>
       <c r="B203" t="n">
-        <v>3.902306165257132</v>
+        <v>4.166043602040112</v>
       </c>
       <c r="C203" t="n">
-        <v>3.902306165257132</v>
+        <v>4.166043602040112</v>
       </c>
     </row>
     <row r="204">
@@ -3747,10 +3747,10 @@
         <v>46072</v>
       </c>
       <c r="B204" t="n">
-        <v>3.8258454923613</v>
+        <v>4.253804257007483</v>
       </c>
       <c r="C204" t="n">
-        <v>3.8258454923613</v>
+        <v>4.253804257007483</v>
       </c>
     </row>
     <row r="205">
@@ -3758,10 +3758,10 @@
         <v>46073</v>
       </c>
       <c r="B205" t="n">
-        <v>4.058132164633558</v>
+        <v>4.329974752951788</v>
       </c>
       <c r="C205" t="n">
-        <v>3.876999476794384</v>
+        <v>4.329974752951788</v>
       </c>
     </row>
     <row r="206">
@@ -3769,10 +3769,10 @@
         <v>46074</v>
       </c>
       <c r="B206" t="n">
-        <v>4.081768560930386</v>
+        <v>4.394864819093815</v>
       </c>
       <c r="C206" t="n">
-        <v>3.958775533261006</v>
+        <v>4.394864819093815</v>
       </c>
     </row>
     <row r="207">
@@ -3780,10 +3780,10 @@
         <v>46075</v>
       </c>
       <c r="B207" t="n">
-        <v>4.19622274623126</v>
+        <v>4.43468103372181</v>
       </c>
       <c r="C207" t="n">
-        <v>4.19622274623126</v>
+        <v>4.43468103372181</v>
       </c>
     </row>
     <row r="208">
@@ -3791,10 +3791,10 @@
         <v>46076</v>
       </c>
       <c r="B208" t="n">
-        <v>4.134925050422338</v>
+        <v>4.339736405169021</v>
       </c>
       <c r="C208" t="n">
-        <v>4.134925050422338</v>
+        <v>4.339736405169021</v>
       </c>
     </row>
     <row r="209">
@@ -3802,10 +3802,10 @@
         <v>46077</v>
       </c>
       <c r="B209" t="n">
-        <v>4.025703650614106</v>
+        <v>4.282272581733713</v>
       </c>
       <c r="C209" t="n">
-        <v>4.025703650614106</v>
+        <v>4.282272581733713</v>
       </c>
     </row>
     <row r="210">
@@ -3813,10 +3813,10 @@
         <v>46078</v>
       </c>
       <c r="B210" t="n">
-        <v>4.085085320398866</v>
+        <v>4.3822703600396</v>
       </c>
       <c r="C210" t="n">
-        <v>4.085085320398866</v>
+        <v>4.3822703600396</v>
       </c>
     </row>
     <row r="211">
@@ -3824,10 +3824,10 @@
         <v>46079</v>
       </c>
       <c r="B211" t="n">
-        <v>4.139763613233502</v>
+        <v>4.301988969619211</v>
       </c>
       <c r="C211" t="n">
-        <v>4.139763613233502</v>
+        <v>4.301988969619211</v>
       </c>
     </row>
     <row r="212">
@@ -3835,10 +3835,10 @@
         <v>46080</v>
       </c>
       <c r="B212" t="n">
-        <v>4.059980304240491</v>
+        <v>4.380159012132893</v>
       </c>
       <c r="C212" t="n">
-        <v>4.059980304240491</v>
+        <v>4.380159012132893</v>
       </c>
     </row>
     <row r="213">
@@ -3846,10 +3846,10 @@
         <v>46081</v>
       </c>
       <c r="B213" t="n">
-        <v>4.218619978455825</v>
+        <v>4.313480972399702</v>
       </c>
       <c r="C213" t="n">
-        <v>4.218619978455825</v>
+        <v>4.313480972399702</v>
       </c>
     </row>
     <row r="214">
@@ -3857,10 +3857,10 @@
         <v>46082</v>
       </c>
       <c r="B214" t="n">
-        <v>4.182418946222087</v>
+        <v>4.372932465119566</v>
       </c>
       <c r="C214" t="n">
-        <v>4.182418946222087</v>
+        <v>4.372932465119566</v>
       </c>
     </row>
     <row r="215">
@@ -3868,10 +3868,10 @@
         <v>46083</v>
       </c>
       <c r="B215" t="n">
-        <v>4.070768989097473</v>
+        <v>4.400037348445281</v>
       </c>
       <c r="C215" t="n">
-        <v>4.070768989097473</v>
+        <v>4.400037348445281</v>
       </c>
     </row>
     <row r="216">
@@ -3879,10 +3879,10 @@
         <v>46084</v>
       </c>
       <c r="B216" t="n">
-        <v>4.120746410058167</v>
+        <v>4.361253267009833</v>
       </c>
       <c r="C216" t="n">
-        <v>4.120746410058167</v>
+        <v>4.361253267009833</v>
       </c>
     </row>
     <row r="217">
@@ -3890,10 +3890,10 @@
         <v>46085</v>
       </c>
       <c r="B217" t="n">
-        <v>4.274222936949494</v>
+        <v>4.389844452377714</v>
       </c>
       <c r="C217" t="n">
-        <v>4.274222936949494</v>
+        <v>4.389844452377714</v>
       </c>
     </row>
     <row r="218">
@@ -3901,10 +3901,10 @@
         <v>46086</v>
       </c>
       <c r="B218" t="n">
-        <v>4.300548046469967</v>
+        <v>4.480516953511975</v>
       </c>
       <c r="C218" t="n">
-        <v>4.300548046469967</v>
+        <v>4.480516953511975</v>
       </c>
     </row>
     <row r="219">
@@ -3912,10 +3912,10 @@
         <v>46087</v>
       </c>
       <c r="B219" t="n">
-        <v>4.184199917134579</v>
+        <v>4.410531864446163</v>
       </c>
       <c r="C219" t="n">
-        <v>4.184199917134579</v>
+        <v>4.410531864446163</v>
       </c>
     </row>
     <row r="220">
@@ -3923,10 +3923,10 @@
         <v>46088</v>
       </c>
       <c r="B220" t="n">
-        <v>4.317512037750612</v>
+        <v>4.486665723899269</v>
       </c>
       <c r="C220" t="n">
-        <v>4.317512037750612</v>
+        <v>4.486665723899269</v>
       </c>
     </row>
     <row r="221">
@@ -3934,10 +3934,10 @@
         <v>46089</v>
       </c>
       <c r="B221" t="n">
-        <v>4.242819395785316</v>
+        <v>4.445365984067113</v>
       </c>
       <c r="C221" t="n">
-        <v>4.242819395785316</v>
+        <v>4.445365984067113</v>
       </c>
     </row>
     <row r="222">
@@ -3945,10 +3945,10 @@
         <v>46090</v>
       </c>
       <c r="B222" t="n">
-        <v>4.283170694105777</v>
+        <v>4.453724094129533</v>
       </c>
       <c r="C222" t="n">
-        <v>4.283170694105777</v>
+        <v>4.453724094129533</v>
       </c>
     </row>
     <row r="223">
@@ -3956,10 +3956,10 @@
         <v>46091</v>
       </c>
       <c r="B223" t="n">
-        <v>4.31956044370342</v>
+        <v>4.508332850765116</v>
       </c>
       <c r="C223" t="n">
-        <v>4.31956044370342</v>
+        <v>4.508332850765116</v>
       </c>
     </row>
     <row r="224">
@@ -3967,10 +3967,10 @@
         <v>46092</v>
       </c>
       <c r="B224" t="n">
-        <v>4.240953349890084</v>
+        <v>4.375033671326444</v>
       </c>
       <c r="C224" t="n">
-        <v>4.240953349890084</v>
+        <v>4.375033671326444</v>
       </c>
     </row>
     <row r="225">
@@ -3978,10 +3978,10 @@
         <v>46093</v>
       </c>
       <c r="B225" t="n">
-        <v>4.200471003907785</v>
+        <v>4.413134920155311</v>
       </c>
       <c r="C225" t="n">
-        <v>4.236246110934294</v>
+        <v>4.413134920155311</v>
       </c>
     </row>
     <row r="226">
@@ -3989,10 +3989,10 @@
         <v>46094</v>
       </c>
       <c r="B226" t="n">
-        <v>4.093515124147229</v>
+        <v>4.380462127396035</v>
       </c>
       <c r="C226" t="n">
-        <v>4.093515124147229</v>
+        <v>4.380462127396035</v>
       </c>
     </row>
     <row r="227">
@@ -4000,10 +4000,10 @@
         <v>46095</v>
       </c>
       <c r="B227" t="n">
-        <v>4.2185915252761</v>
+        <v>4.361351984113346</v>
       </c>
       <c r="C227" t="n">
-        <v>4.2185915252761</v>
+        <v>4.361351984113346</v>
       </c>
     </row>
     <row r="228">
@@ -4011,10 +4011,10 @@
         <v>46096</v>
       </c>
       <c r="B228" t="n">
-        <v>4.15757673704978</v>
+        <v>4.27585656017375</v>
       </c>
       <c r="C228" t="n">
-        <v>4.15757673704978</v>
+        <v>4.27585656017375</v>
       </c>
     </row>
     <row r="229">
@@ -4022,10 +4022,10 @@
         <v>46097</v>
       </c>
       <c r="B229" t="n">
-        <v>4.20443115421398</v>
+        <v>4.240806226857287</v>
       </c>
       <c r="C229" t="n">
-        <v>4.20443115421398</v>
+        <v>4.240806226857287</v>
       </c>
     </row>
     <row r="230">
@@ -4033,10 +4033,10 @@
         <v>46098</v>
       </c>
       <c r="B230" t="n">
-        <v>4.286721476547923</v>
+        <v>4.362811230674385</v>
       </c>
       <c r="C230" t="n">
-        <v>4.286721476547923</v>
+        <v>4.362811230674385</v>
       </c>
     </row>
     <row r="231">
@@ -4044,10 +4044,10 @@
         <v>46099</v>
       </c>
       <c r="B231" t="n">
-        <v>4.299584594615131</v>
+        <v>4.437812816364118</v>
       </c>
       <c r="C231" t="n">
-        <v>4.299584594615131</v>
+        <v>4.437812816364118</v>
       </c>
     </row>
     <row r="232">
@@ -4055,10 +4055,10 @@
         <v>46100</v>
       </c>
       <c r="B232" t="n">
-        <v>4.297917985055426</v>
+        <v>4.443634205664828</v>
       </c>
       <c r="C232" t="n">
-        <v>4.297917985055426</v>
+        <v>4.443634205664828</v>
       </c>
     </row>
     <row r="233">
@@ -4066,10 +4066,10 @@
         <v>46101</v>
       </c>
       <c r="B233" t="n">
-        <v>4.248816058896539</v>
+        <v>4.393358887650846</v>
       </c>
       <c r="C233" t="n">
-        <v>4.248816058896539</v>
+        <v>4.393358887650846</v>
       </c>
     </row>
     <row r="234">
@@ -4077,10 +4077,10 @@
         <v>46102</v>
       </c>
       <c r="B234" t="n">
-        <v>4.183366154246132</v>
+        <v>4.316168804213199</v>
       </c>
       <c r="C234" t="n">
-        <v>4.165458852913863</v>
+        <v>4.316168804213199</v>
       </c>
     </row>
     <row r="235">
@@ -4088,10 +4088,10 @@
         <v>46103</v>
       </c>
       <c r="B235" t="n">
-        <v>3.830612216833684</v>
+        <v>3.829216383692828</v>
       </c>
       <c r="C235" t="n">
-        <v>3.830612216833684</v>
+        <v>4.137866466721963</v>
       </c>
     </row>
     <row r="236">
@@ -4099,10 +4099,10 @@
         <v>46104</v>
       </c>
       <c r="B236" t="n">
-        <v>4.084922873165588</v>
+        <v>4.277394430939918</v>
       </c>
       <c r="C236" t="n">
-        <v>4.15323295768219</v>
+        <v>4.351349039109907</v>
       </c>
     </row>
     <row r="237">
@@ -4110,10 +4110,10 @@
         <v>46105</v>
       </c>
       <c r="B237" t="n">
-        <v>4.105774322511513</v>
+        <v>4.255727061512628</v>
       </c>
       <c r="C237" t="n">
-        <v>4.134061634435174</v>
+        <v>4.300941620347608</v>
       </c>
     </row>
     <row r="238">
@@ -4121,10 +4121,10 @@
         <v>46106</v>
       </c>
       <c r="B238" t="n">
-        <v>4.155273588987823</v>
+        <v>4.288328682649125</v>
       </c>
       <c r="C238" t="n">
-        <v>4.155273588987823</v>
+        <v>4.288328682649125</v>
       </c>
     </row>
     <row r="239">
@@ -4132,10 +4132,10 @@
         <v>46107</v>
       </c>
       <c r="B239" t="n">
-        <v>4.281608602796628</v>
+        <v>4.339900450666143</v>
       </c>
       <c r="C239" t="n">
-        <v>4.281608602796628</v>
+        <v>4.339900450666143</v>
       </c>
     </row>
     <row r="240">
@@ -4143,10 +4143,10 @@
         <v>46108</v>
       </c>
       <c r="B240" t="n">
-        <v>4.07471696450994</v>
+        <v>4.375269176703401</v>
       </c>
       <c r="C240" t="n">
-        <v>4.07471696450994</v>
+        <v>4.375269176703401</v>
       </c>
     </row>
     <row r="241">
@@ -4154,10 +4154,10 @@
         <v>46109</v>
       </c>
       <c r="B241" t="n">
-        <v>4.124103900225701</v>
+        <v>4.400371626682975</v>
       </c>
       <c r="C241" t="n">
-        <v>4.124103900225701</v>
+        <v>4.400371626682975</v>
       </c>
     </row>
     <row r="242">
@@ -4165,10 +4165,10 @@
         <v>46110</v>
       </c>
       <c r="B242" t="n">
-        <v>4.224795936213562</v>
+        <v>4.411923105903027</v>
       </c>
       <c r="C242" t="n">
-        <v>4.224795936213562</v>
+        <v>4.411923105903027</v>
       </c>
     </row>
     <row r="243">
@@ -4176,10 +4176,10 @@
         <v>46111</v>
       </c>
       <c r="B243" t="n">
-        <v>4.304795245284662</v>
+        <v>4.381824287198912</v>
       </c>
       <c r="C243" t="n">
-        <v>4.304795245284662</v>
+        <v>4.381824287198912</v>
       </c>
     </row>
     <row r="244">
@@ -4187,10 +4187,10 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>4.276007754973902</v>
+        <v>4.399987097672689</v>
       </c>
       <c r="C244" t="n">
-        <v>4.276007754973902</v>
+        <v>4.399987097672689</v>
       </c>
     </row>
     <row r="245">
@@ -4198,10 +4198,10 @@
         <v>46113</v>
       </c>
       <c r="B245" t="n">
-        <v>4.192887309121231</v>
+        <v>4.423009134906216</v>
       </c>
       <c r="C245" t="n">
-        <v>4.192887309121231</v>
+        <v>4.423009134906216</v>
       </c>
     </row>
     <row r="246">
@@ -4209,10 +4209,10 @@
         <v>46114</v>
       </c>
       <c r="B246" t="n">
-        <v>4.220088651261786</v>
+        <v>4.406015159075779</v>
       </c>
       <c r="C246" t="n">
-        <v>4.220088651261786</v>
+        <v>4.406015159075779</v>
       </c>
     </row>
     <row r="247">
@@ -4220,10 +4220,10 @@
         <v>46115</v>
       </c>
       <c r="B247" t="n">
-        <v>4.082937277091625</v>
+        <v>4.430568963901477</v>
       </c>
       <c r="C247" t="n">
-        <v>4.082937277091625</v>
+        <v>4.430568963901477</v>
       </c>
     </row>
     <row r="248">
@@ -4231,10 +4231,10 @@
         <v>46116</v>
       </c>
       <c r="B248" t="n">
-        <v>4.117697323320911</v>
+        <v>4.22752948671531</v>
       </c>
       <c r="C248" t="n">
-        <v>4.117697323320911</v>
+        <v>4.22752948671531</v>
       </c>
     </row>
     <row r="249">
@@ -4242,10 +4242,10 @@
         <v>46117</v>
       </c>
       <c r="B249" t="n">
-        <v>3.974625304486533</v>
+        <v>4.321276747079891</v>
       </c>
       <c r="C249" t="n">
-        <v>3.974625304486533</v>
+        <v>4.321276747079891</v>
       </c>
     </row>
     <row r="250">
@@ -4253,10 +4253,10 @@
         <v>46118</v>
       </c>
       <c r="B250" t="n">
-        <v>4.066604995583614</v>
+        <v>4.367961969537408</v>
       </c>
       <c r="C250" t="n">
-        <v>4.066604995583614</v>
+        <v>4.367961969537408</v>
       </c>
     </row>
     <row r="251">
@@ -4264,10 +4264,10 @@
         <v>46119</v>
       </c>
       <c r="B251" t="n">
-        <v>4.100637613722056</v>
+        <v>4.394948134322497</v>
       </c>
       <c r="C251" t="n">
-        <v>4.100637613722056</v>
+        <v>4.394948134322497</v>
       </c>
     </row>
     <row r="252">
@@ -4275,10 +4275,10 @@
         <v>46120</v>
       </c>
       <c r="B252" t="n">
-        <v>4.195249121592188</v>
+        <v>4.339321391075468</v>
       </c>
       <c r="C252" t="n">
-        <v>4.195249121592188</v>
+        <v>4.339321391075468</v>
       </c>
     </row>
     <row r="253">
@@ -4286,10 +4286,10 @@
         <v>46121</v>
       </c>
       <c r="B253" t="n">
-        <v>4.123829977551589</v>
+        <v>4.400544837456148</v>
       </c>
       <c r="C253" t="n">
-        <v>4.123829977551589</v>
+        <v>4.400544837456148</v>
       </c>
     </row>
     <row r="254">
@@ -4297,10 +4297,10 @@
         <v>46122</v>
       </c>
       <c r="B254" t="n">
-        <v>4.047329563824642</v>
+        <v>4.272252286084704</v>
       </c>
       <c r="C254" t="n">
-        <v>4.047329563824642</v>
+        <v>4.272252286084704</v>
       </c>
     </row>
     <row r="255">
@@ -4308,10 +4308,10 @@
         <v>46123</v>
       </c>
       <c r="B255" t="n">
-        <v>4.119871098795379</v>
+        <v>4.391381372384599</v>
       </c>
       <c r="C255" t="n">
-        <v>4.125981468213463</v>
+        <v>4.381300735889687</v>
       </c>
     </row>
     <row r="256">
@@ -4319,10 +4319,10 @@
         <v>46124</v>
       </c>
       <c r="B256" t="n">
-        <v>4.100943741315564</v>
+        <v>4.411435329640704</v>
       </c>
       <c r="C256" t="n">
-        <v>3.987472830869542</v>
+        <v>4.301666949172199</v>
       </c>
     </row>
     <row r="257">
@@ -4330,10 +4330,10 @@
         <v>46125</v>
       </c>
       <c r="B257" t="n">
-        <v>4.30862450429229</v>
+        <v>4.398262356472682</v>
       </c>
       <c r="C257" t="n">
-        <v>4.05620748278287</v>
+        <v>4.358362233483422</v>
       </c>
     </row>
   </sheetData>
@@ -4450,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0009257050093935959</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.07411631529028861</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -4497,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.272601238639913</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1691683683500593</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04347275263830142</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.09313998739569751</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.341359297718177</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1280121726962089</v>
+        <v>-0.1616178762155545</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.214689487939232</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -4779,10 +4779,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.321256242340628</v>
+        <v>-1.383455296302706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1584207700726341</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.05311317960899142</v>
+        <v>-1.884766613022853</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4572459216819711</v>
+        <v>-1.984767946240831</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.07004566582103244</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07111008896457616</v>
+        <v>0.001353273583983849</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3464762842743681</v>
+        <v>-0.2210796174963243</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1695976813447557</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1977832685970471</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3537465945929981</v>
+        <v>-0.2574626654708605</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -5002,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09862858320093082</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01920681901646759</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.05614403822640845</v>
+        <v>-0.06681131784710992</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06533932455564706</v>
+        <v>-0.02299988776696527</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07992672732081818</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -5140,10 +5140,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1849247838159398</v>
+        <v>-0.3118714692315856</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2045126141617675</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.024964165549898</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2452708346316266</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.171959939103508</v>
+        <v>-0.1877290305792663</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1229944815205228</v>
+        <v>-0.2107052946483803</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.172151238058758</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.06173150958864948</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2751981488860658</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1203272129147432</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2155516890422344</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01458334817446616</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -5355,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1905438750291162</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -5375,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.04598426067503203</v>
+        <v>-0.000963095548613957</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -5390,10 +5390,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.05176015259108802</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.004319561074888512</v>
+        <v>-0.09307032545313376</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1545614808672546</v>
+        <v>-0.02226755157607663</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5422,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.07442952637767153</v>
+        <v>-0.04664503007654197</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.01646049599529498</v>
+        <v>-0.04992457384919469</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -5487,13 +5487,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.06793359993143477</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6198057052825585</v>
+        <v>-0.4104659992706736</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0.004902588951243736</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.01131274004057747</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-0.008737231862160577</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1592873874563288</v>
+        <v>0.03373319012008924</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.06967151260919513</v>
+        <v>-0.1031848837166507</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.01381541077269866</v>
+        <v>-0.002642915570111093</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -5751,10 +5751,10 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1056253411344312</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1781719108697937</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.005350435698299627</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -5784,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.05813293745186643</v>
+        <v>0.05960246771872324</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.02119674111560332</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.09864444678363293</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -5822,16 +5822,16 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.3990961190198963</v>
+        <v>-0.1344820930893578</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.2889281151370882</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.1287478470450845</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1563708137509043</v>
+        <v>0.4639505789299041</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1476804578287281</v>
+        <v>0.4251598060668353</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.02064601292895585</v>
+        <v>0.1646629074437911</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -6010,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1070301087433214</v>
+        <v>0.5595534567218676</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.07309567739770495</v>
+        <v>0.1298102213336221</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1023121695954741</v>
+        <v>0.5686849621369348</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -6127,10 +6127,10 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5368216070267993</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.317412600119515</v>
+        <v>-0.5004947152539279</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -6151,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.02656818924417559</v>
+        <v>0.191135583662712</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2027852365413692</v>
+        <v>0.4292052252844782</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV12_v11_vs_strictV1_hero_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV12_v11_vs_strictV1_hero_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -655,24 +655,24 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DO_2_4</t>
+          <t>DO_1_3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.912939936395083</v>
+        <v>4.403560302427994</v>
       </c>
       <c r="D5" t="n">
-        <v>3.907149817565858</v>
+        <v>4.398000079696054</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.005790118829224866</v>
+        <v>-0.005560222731940456</v>
       </c>
       <c r="F5" t="n">
-        <v>1.726946888237211</v>
+        <v>0.8634734441186055</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>98.27305311176279</v>
+        <v>99.1365265558814</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -695,24 +695,24 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>DO_2_4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.403560302427994</v>
+        <v>3.842625485715068</v>
       </c>
       <c r="D6" t="n">
-        <v>4.398000079696054</v>
+        <v>3.841556184464346</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005560222731940456</v>
+        <v>-0.001069301250721466</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8634734441186055</v>
+        <v>1.726946888237211</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>99.1365265558814</v>
+        <v>98.27305311176279</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.563756091682329</v>
+        <v>4.564449796052591</v>
       </c>
       <c r="D7" t="n">
-        <v>4.563756091682329</v>
+        <v>4.564449796052591</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.2660466998305</v>
+        <v>4.298169168604909</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2660466998305</v>
+        <v>4.298169168604909</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.77875693485721</v>
+        <v>3.77816407661268</v>
       </c>
       <c r="D15" t="n">
-        <v>3.818303496684228</v>
+        <v>3.815900453814672</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03954656182701788</v>
+        <v>0.03773637720199163</v>
       </c>
       <c r="F15" t="n">
         <v>2.036493971977843</v>
@@ -1078,16 +1078,16 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="H15" t="n">
-        <v>8.031932225480611</v>
+        <v>7.917888563049853</v>
       </c>
       <c r="I15" t="n">
-        <v>1.319648093841642</v>
+        <v>1.417399804496579</v>
       </c>
       <c r="J15" t="n">
         <v>1.01010101010101</v>
       </c>
       <c r="K15" t="n">
-        <v>86.77093515803193</v>
+        <v>86.78722710980776</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86.77093515803193</v>
+        <v>86.78722710980776</v>
       </c>
       <c r="C11" t="n">
         <v>2.036493971977843</v>
@@ -1380,10 +1380,10 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="E11" t="n">
-        <v>8.031932225480611</v>
+        <v>7.917888563049853</v>
       </c>
       <c r="F11" t="n">
-        <v>1.319648093841642</v>
+        <v>1.417399804496579</v>
       </c>
       <c r="G11" t="n">
         <v>1.01010101010101</v>
@@ -1525,10 +1525,10 @@
         <v>45870</v>
       </c>
       <c r="B2" t="n">
-        <v>4.550806778696802</v>
+        <v>4.550224352825955</v>
       </c>
       <c r="C2" t="n">
-        <v>4.550806778696802</v>
+        <v>4.550224352825955</v>
       </c>
     </row>
     <row r="3">
@@ -1536,10 +1536,10 @@
         <v>45871</v>
       </c>
       <c r="B3" t="n">
-        <v>4.491290992217966</v>
+        <v>4.487274015997287</v>
       </c>
       <c r="C3" t="n">
-        <v>4.491290992217966</v>
+        <v>4.487274015997287</v>
       </c>
     </row>
     <row r="4">
@@ -1547,10 +1547,10 @@
         <v>45872</v>
       </c>
       <c r="B4" t="n">
-        <v>4.478801406810811</v>
+        <v>4.481030912318834</v>
       </c>
       <c r="C4" t="n">
-        <v>4.478801406810811</v>
+        <v>4.481030912318834</v>
       </c>
     </row>
     <row r="5">
@@ -1580,10 +1580,10 @@
         <v>45875</v>
       </c>
       <c r="B7" t="n">
-        <v>4.408090474787095</v>
+        <v>4.413361523436685</v>
       </c>
       <c r="C7" t="n">
-        <v>4.408090474787095</v>
+        <v>4.413361523436685</v>
       </c>
     </row>
     <row r="8">
@@ -1613,10 +1613,10 @@
         <v>45878</v>
       </c>
       <c r="B10" t="n">
-        <v>4.480590462045601</v>
+        <v>4.479900505569375</v>
       </c>
       <c r="C10" t="n">
-        <v>4.480590462045601</v>
+        <v>4.479900505569375</v>
       </c>
     </row>
     <row r="11">
@@ -1624,10 +1624,10 @@
         <v>45879</v>
       </c>
       <c r="B11" t="n">
-        <v>4.402031425226692</v>
+        <v>4.394382318166747</v>
       </c>
       <c r="C11" t="n">
-        <v>4.402031425226692</v>
+        <v>4.394382318166747</v>
       </c>
     </row>
     <row r="12">
@@ -1635,10 +1635,10 @@
         <v>45880</v>
       </c>
       <c r="B12" t="n">
-        <v>4.499279912871334</v>
+        <v>4.490627704269115</v>
       </c>
       <c r="C12" t="n">
-        <v>4.499279912871334</v>
+        <v>4.490627704269115</v>
       </c>
     </row>
     <row r="13">
@@ -1646,10 +1646,10 @@
         <v>45881</v>
       </c>
       <c r="B13" t="n">
-        <v>4.495914263102534</v>
+        <v>4.496012361867365</v>
       </c>
       <c r="C13" t="n">
-        <v>4.495914263102534</v>
+        <v>4.496012361867365</v>
       </c>
     </row>
     <row r="14">
@@ -1668,10 +1668,10 @@
         <v>45883</v>
       </c>
       <c r="B15" t="n">
-        <v>4.505430730505763</v>
+        <v>4.505919734029605</v>
       </c>
       <c r="C15" t="n">
-        <v>4.505430730505763</v>
+        <v>4.505919734029605</v>
       </c>
     </row>
     <row r="16">
@@ -1690,10 +1690,10 @@
         <v>45885</v>
       </c>
       <c r="B17" t="n">
-        <v>4.471558351779957</v>
+        <v>4.471027590475191</v>
       </c>
       <c r="C17" t="n">
-        <v>4.471558351779957</v>
+        <v>4.471027590475191</v>
       </c>
     </row>
     <row r="18">
@@ -1734,10 +1734,10 @@
         <v>45889</v>
       </c>
       <c r="B21" t="n">
-        <v>4.4612431098102</v>
+        <v>4.460402175304885</v>
       </c>
       <c r="C21" t="n">
-        <v>4.4612431098102</v>
+        <v>4.460402175304885</v>
       </c>
     </row>
     <row r="22">
@@ -1745,10 +1745,10 @@
         <v>45890</v>
       </c>
       <c r="B22" t="n">
-        <v>4.445562082826374</v>
+        <v>4.4443506483723</v>
       </c>
       <c r="C22" t="n">
-        <v>4.445562082826374</v>
+        <v>4.4443506483723</v>
       </c>
     </row>
     <row r="23">
@@ -1756,10 +1756,10 @@
         <v>45891</v>
       </c>
       <c r="B23" t="n">
-        <v>4.465829857443206</v>
+        <v>4.465982351335026</v>
       </c>
       <c r="C23" t="n">
-        <v>4.465829857443206</v>
+        <v>4.465982351335026</v>
       </c>
     </row>
     <row r="24">
@@ -1767,10 +1767,10 @@
         <v>45892</v>
       </c>
       <c r="B24" t="n">
-        <v>4.459156774747385</v>
+        <v>4.458579577425594</v>
       </c>
       <c r="C24" t="n">
-        <v>4.459156774747385</v>
+        <v>4.458579577425594</v>
       </c>
     </row>
     <row r="25">
@@ -1778,10 +1778,10 @@
         <v>45893</v>
       </c>
       <c r="B25" t="n">
-        <v>4.44627033293506</v>
+        <v>4.447117322406552</v>
       </c>
       <c r="C25" t="n">
-        <v>4.44627033293506</v>
+        <v>4.447117322406552</v>
       </c>
     </row>
     <row r="26">
@@ -1789,10 +1789,10 @@
         <v>45894</v>
       </c>
       <c r="B26" t="n">
-        <v>4.453616463275117</v>
+        <v>4.449883169376089</v>
       </c>
       <c r="C26" t="n">
-        <v>4.453616463275117</v>
+        <v>4.449883169376089</v>
       </c>
     </row>
     <row r="27">
@@ -1800,10 +1800,10 @@
         <v>45895</v>
       </c>
       <c r="B27" t="n">
-        <v>4.452755920096219</v>
+        <v>4.454616175611742</v>
       </c>
       <c r="C27" t="n">
-        <v>4.452755920096219</v>
+        <v>4.454616175611742</v>
       </c>
     </row>
     <row r="28">
@@ -1811,10 +1811,10 @@
         <v>45896</v>
       </c>
       <c r="B28" t="n">
-        <v>4.454567572073698</v>
+        <v>4.454097487182596</v>
       </c>
       <c r="C28" t="n">
-        <v>4.454567572073698</v>
+        <v>4.454097487182596</v>
       </c>
     </row>
     <row r="29">
@@ -1822,10 +1822,10 @@
         <v>45897</v>
       </c>
       <c r="B29" t="n">
-        <v>4.440863485213735</v>
+        <v>4.440343617132173</v>
       </c>
       <c r="C29" t="n">
-        <v>4.440863485213735</v>
+        <v>4.440343617132173</v>
       </c>
     </row>
     <row r="30">
@@ -1833,10 +1833,10 @@
         <v>45898</v>
       </c>
       <c r="B30" t="n">
-        <v>4.491093458222737</v>
+        <v>4.487232880794032</v>
       </c>
       <c r="C30" t="n">
-        <v>4.491093458222737</v>
+        <v>4.487232880794032</v>
       </c>
     </row>
     <row r="31">
@@ -1844,10 +1844,10 @@
         <v>45899</v>
       </c>
       <c r="B31" t="n">
-        <v>4.4768385905326</v>
+        <v>4.476885851617885</v>
       </c>
       <c r="C31" t="n">
-        <v>4.4768385905326</v>
+        <v>4.476885851617885</v>
       </c>
     </row>
     <row r="32">
@@ -1866,10 +1866,10 @@
         <v>45901</v>
       </c>
       <c r="B33" t="n">
-        <v>4.468259184064085</v>
+        <v>4.470007236864381</v>
       </c>
       <c r="C33" t="n">
-        <v>4.468259184064085</v>
+        <v>4.470007236864381</v>
       </c>
     </row>
     <row r="34">
@@ -1888,10 +1888,10 @@
         <v>45903</v>
       </c>
       <c r="B35" t="n">
-        <v>4.441979492270363</v>
+        <v>4.442087280367484</v>
       </c>
       <c r="C35" t="n">
-        <v>4.441979492270363</v>
+        <v>4.442087280367484</v>
       </c>
     </row>
     <row r="36">
@@ -1910,10 +1910,10 @@
         <v>45905</v>
       </c>
       <c r="B37" t="n">
-        <v>4.453720267231112</v>
+        <v>4.453567809772963</v>
       </c>
       <c r="C37" t="n">
-        <v>4.453720267231112</v>
+        <v>4.453567809772963</v>
       </c>
     </row>
     <row r="38">
@@ -1932,10 +1932,10 @@
         <v>45907</v>
       </c>
       <c r="B39" t="n">
-        <v>4.4228126715486</v>
+        <v>4.425546491842271</v>
       </c>
       <c r="C39" t="n">
-        <v>4.4228126715486</v>
+        <v>4.425546491842271</v>
       </c>
     </row>
     <row r="40">
@@ -1943,10 +1943,10 @@
         <v>45908</v>
       </c>
       <c r="B40" t="n">
-        <v>4.416545834477949</v>
+        <v>4.418169187058433</v>
       </c>
       <c r="C40" t="n">
-        <v>4.416545834477949</v>
+        <v>4.418169187058433</v>
       </c>
     </row>
     <row r="41">
@@ -1954,10 +1954,10 @@
         <v>45909</v>
       </c>
       <c r="B41" t="n">
-        <v>4.354577133937146</v>
+        <v>4.357240250776663</v>
       </c>
       <c r="C41" t="n">
-        <v>4.354577133937146</v>
+        <v>4.357240250776663</v>
       </c>
     </row>
     <row r="42">
@@ -1987,10 +1987,10 @@
         <v>45912</v>
       </c>
       <c r="B44" t="n">
-        <v>4.198253575896558</v>
+        <v>4.171619943272933</v>
       </c>
       <c r="C44" t="n">
-        <v>4.198253575896558</v>
+        <v>4.171619943272933</v>
       </c>
     </row>
     <row r="45">
@@ -2020,10 +2020,10 @@
         <v>45915</v>
       </c>
       <c r="B47" t="n">
-        <v>4.358607989178887</v>
+        <v>4.334781059415009</v>
       </c>
       <c r="C47" t="n">
-        <v>4.358607989178887</v>
+        <v>4.334781059415009</v>
       </c>
     </row>
     <row r="48">
@@ -2031,10 +2031,10 @@
         <v>45916</v>
       </c>
       <c r="B48" t="n">
-        <v>4.414200419818424</v>
+        <v>4.421703721952776</v>
       </c>
       <c r="C48" t="n">
-        <v>4.414200419818424</v>
+        <v>4.421703721952776</v>
       </c>
     </row>
     <row r="49">
@@ -2042,10 +2042,10 @@
         <v>45917</v>
       </c>
       <c r="B49" t="n">
-        <v>4.246423975112271</v>
+        <v>4.24176637224477</v>
       </c>
       <c r="C49" t="n">
-        <v>4.246423975112271</v>
+        <v>4.24176637224477</v>
       </c>
     </row>
     <row r="50">
@@ -2053,10 +2053,10 @@
         <v>45918</v>
       </c>
       <c r="B50" t="n">
-        <v>4.345928957272575</v>
+        <v>4.35969260338428</v>
       </c>
       <c r="C50" t="n">
-        <v>4.345928957272575</v>
+        <v>4.35969260338428</v>
       </c>
     </row>
     <row r="51">
@@ -2064,10 +2064,10 @@
         <v>45919</v>
       </c>
       <c r="B51" t="n">
-        <v>4.298312644451833</v>
+        <v>4.286361930245635</v>
       </c>
       <c r="C51" t="n">
-        <v>4.298312644451833</v>
+        <v>4.286361930245635</v>
       </c>
     </row>
     <row r="52">
@@ -2130,10 +2130,10 @@
         <v>45925</v>
       </c>
       <c r="B57" t="n">
-        <v>4.475814430074523</v>
+        <v>4.476736318670667</v>
       </c>
       <c r="C57" t="n">
-        <v>4.475814430074523</v>
+        <v>4.476736318670667</v>
       </c>
     </row>
     <row r="58">
@@ -2163,10 +2163,10 @@
         <v>45928</v>
       </c>
       <c r="B60" t="n">
-        <v>4.392820960362134</v>
+        <v>4.402712320380793</v>
       </c>
       <c r="C60" t="n">
-        <v>4.379739220757669</v>
+        <v>4.402712320380793</v>
       </c>
     </row>
     <row r="61">
@@ -2199,7 +2199,7 @@
         <v>4.448622727169796</v>
       </c>
       <c r="C63" t="n">
-        <v>4.44711206922393</v>
+        <v>4.445878694670469</v>
       </c>
     </row>
     <row r="64">
@@ -2240,10 +2240,10 @@
         <v>45935</v>
       </c>
       <c r="B67" t="n">
-        <v>4.424628732516729</v>
+        <v>4.411849770868091</v>
       </c>
       <c r="C67" t="n">
-        <v>4.404616520615223</v>
+        <v>4.397244139972154</v>
       </c>
     </row>
     <row r="68">
@@ -2251,10 +2251,10 @@
         <v>45936</v>
       </c>
       <c r="B68" t="n">
-        <v>4.448154833696002</v>
+        <v>4.449241046956155</v>
       </c>
       <c r="C68" t="n">
-        <v>4.40788505865124</v>
+        <v>4.410950912811506</v>
       </c>
     </row>
     <row r="69">
@@ -2273,10 +2273,10 @@
         <v>45938</v>
       </c>
       <c r="B70" t="n">
+        <v>4.426824640341</v>
+      </c>
+      <c r="C70" t="n">
         <v>4.419838501395427</v>
-      </c>
-      <c r="C70" t="n">
-        <v>4.412776657713051</v>
       </c>
     </row>
     <row r="71">
@@ -2284,10 +2284,10 @@
         <v>45939</v>
       </c>
       <c r="B71" t="n">
-        <v>4.460460167174654</v>
+        <v>4.456774259182428</v>
       </c>
       <c r="C71" t="n">
-        <v>4.460460167174654</v>
+        <v>4.456774259182428</v>
       </c>
     </row>
     <row r="72">
@@ -2317,10 +2317,10 @@
         <v>45942</v>
       </c>
       <c r="B74" t="n">
-        <v>4.431580415001976</v>
+        <v>4.431363088722703</v>
       </c>
       <c r="C74" t="n">
-        <v>4.431580415001976</v>
+        <v>4.431363088722703</v>
       </c>
     </row>
     <row r="75">
@@ -2339,10 +2339,10 @@
         <v>45944</v>
       </c>
       <c r="B76" t="n">
-        <v>4.412622953155796</v>
+        <v>4.431995228014618</v>
       </c>
       <c r="C76" t="n">
-        <v>4.412622953155796</v>
+        <v>4.431995228014618</v>
       </c>
     </row>
     <row r="77">
@@ -2350,10 +2350,10 @@
         <v>45945</v>
       </c>
       <c r="B77" t="n">
-        <v>4.404266812625424</v>
+        <v>4.400411913064367</v>
       </c>
       <c r="C77" t="n">
-        <v>4.404266812625424</v>
+        <v>4.400411913064367</v>
       </c>
     </row>
     <row r="78">
@@ -2383,10 +2383,10 @@
         <v>45948</v>
       </c>
       <c r="B80" t="n">
-        <v>4.44765694234237</v>
+        <v>4.445853172358282</v>
       </c>
       <c r="C80" t="n">
-        <v>4.44765694234237</v>
+        <v>4.445853172358282</v>
       </c>
     </row>
     <row r="81">
@@ -2405,10 +2405,10 @@
         <v>45950</v>
       </c>
       <c r="B82" t="n">
-        <v>4.383965965080968</v>
+        <v>4.365892253868493</v>
       </c>
       <c r="C82" t="n">
-        <v>4.383965965080968</v>
+        <v>4.365892253868493</v>
       </c>
     </row>
     <row r="83">
@@ -2438,10 +2438,10 @@
         <v>45953</v>
       </c>
       <c r="B85" t="n">
-        <v>4.279615739044174</v>
+        <v>4.298204422537197</v>
       </c>
       <c r="C85" t="n">
-        <v>4.279615739044174</v>
+        <v>4.298204422537197</v>
       </c>
     </row>
     <row r="86">
@@ -2460,10 +2460,10 @@
         <v>45955</v>
       </c>
       <c r="B87" t="n">
-        <v>4.351268419973931</v>
+        <v>4.358832775795633</v>
       </c>
       <c r="C87" t="n">
-        <v>4.351268419973931</v>
+        <v>4.358832775795633</v>
       </c>
     </row>
     <row r="88">
@@ -2471,10 +2471,10 @@
         <v>45956</v>
       </c>
       <c r="B88" t="n">
-        <v>4.416673184471487</v>
+        <v>4.418019337083566</v>
       </c>
       <c r="C88" t="n">
-        <v>4.416673184471487</v>
+        <v>4.418019337083566</v>
       </c>
     </row>
     <row r="89">
@@ -2482,10 +2482,10 @@
         <v>45957</v>
       </c>
       <c r="B89" t="n">
-        <v>4.396581619579717</v>
+        <v>4.401563251480535</v>
       </c>
       <c r="C89" t="n">
-        <v>4.396581619579717</v>
+        <v>4.401563251480535</v>
       </c>
     </row>
     <row r="90">
@@ -2493,10 +2493,10 @@
         <v>45958</v>
       </c>
       <c r="B90" t="n">
-        <v>4.284868802327406</v>
+        <v>4.281225186501011</v>
       </c>
       <c r="C90" t="n">
-        <v>4.284868802327406</v>
+        <v>4.281225186501011</v>
       </c>
     </row>
     <row r="91">
@@ -2526,10 +2526,10 @@
         <v>45961</v>
       </c>
       <c r="B93" t="n">
-        <v>4.381765006724674</v>
+        <v>4.377503903996358</v>
       </c>
       <c r="C93" t="n">
-        <v>4.381765006724674</v>
+        <v>4.377503903996358</v>
       </c>
     </row>
     <row r="94">
@@ -2537,10 +2537,10 @@
         <v>45962</v>
       </c>
       <c r="B94" t="n">
-        <v>4.431240771847746</v>
+        <v>4.427453938521518</v>
       </c>
       <c r="C94" t="n">
-        <v>4.431240771847746</v>
+        <v>4.427453938521518</v>
       </c>
     </row>
     <row r="95">
@@ -2548,10 +2548,10 @@
         <v>45963</v>
       </c>
       <c r="B95" t="n">
-        <v>4.400752841431887</v>
+        <v>4.404832462121337</v>
       </c>
       <c r="C95" t="n">
-        <v>4.400752841431887</v>
+        <v>4.404832462121337</v>
       </c>
     </row>
     <row r="96">
@@ -2559,10 +2559,10 @@
         <v>45964</v>
       </c>
       <c r="B96" t="n">
-        <v>4.393748259562787</v>
+        <v>4.39380076976802</v>
       </c>
       <c r="C96" t="n">
-        <v>4.393748259562787</v>
+        <v>4.39380076976802</v>
       </c>
     </row>
     <row r="97">
@@ -2570,10 +2570,10 @@
         <v>45965</v>
       </c>
       <c r="B97" t="n">
-        <v>4.394733357413747</v>
+        <v>4.380791362066857</v>
       </c>
       <c r="C97" t="n">
-        <v>4.394733357413747</v>
+        <v>4.380791362066857</v>
       </c>
     </row>
     <row r="98">
@@ -2592,10 +2592,10 @@
         <v>45967</v>
       </c>
       <c r="B99" t="n">
-        <v>4.305837462677302</v>
+        <v>4.241055947921868</v>
       </c>
       <c r="C99" t="n">
-        <v>4.305837462677302</v>
+        <v>4.241055947921868</v>
       </c>
     </row>
     <row r="100">
@@ -2614,10 +2614,10 @@
         <v>45969</v>
       </c>
       <c r="B101" t="n">
-        <v>4.419568650164198</v>
+        <v>4.421440978745439</v>
       </c>
       <c r="C101" t="n">
-        <v>4.419568650164198</v>
+        <v>4.421440978745439</v>
       </c>
     </row>
     <row r="102">
@@ -2647,10 +2647,10 @@
         <v>45972</v>
       </c>
       <c r="B104" t="n">
-        <v>4.373676454870157</v>
+        <v>4.349293241040953</v>
       </c>
       <c r="C104" t="n">
-        <v>4.373676454870157</v>
+        <v>4.349293241040953</v>
       </c>
     </row>
     <row r="105">
@@ -2658,10 +2658,10 @@
         <v>45973</v>
       </c>
       <c r="B105" t="n">
-        <v>4.323720021249467</v>
+        <v>4.292523592832386</v>
       </c>
       <c r="C105" t="n">
-        <v>4.332217008913166</v>
+        <v>4.301020580496085</v>
       </c>
     </row>
     <row r="106">
@@ -2669,10 +2669,10 @@
         <v>45974</v>
       </c>
       <c r="B106" t="n">
-        <v>4.351127614559865</v>
+        <v>4.346570490092844</v>
       </c>
       <c r="C106" t="n">
-        <v>4.351127614559865</v>
+        <v>4.346570490092844</v>
       </c>
     </row>
     <row r="107">
@@ -2691,10 +2691,10 @@
         <v>45976</v>
       </c>
       <c r="B108" t="n">
-        <v>4.359909627016278</v>
+        <v>4.361982663937962</v>
       </c>
       <c r="C108" t="n">
-        <v>4.359909627016278</v>
+        <v>4.361982663937962</v>
       </c>
     </row>
     <row r="109">
@@ -2768,10 +2768,10 @@
         <v>45983</v>
       </c>
       <c r="B115" t="n">
-        <v>4.407953126029099</v>
+        <v>4.400454643179666</v>
       </c>
       <c r="C115" t="n">
-        <v>4.407953126029099</v>
+        <v>4.400454643179666</v>
       </c>
     </row>
     <row r="116">
@@ -2779,10 +2779,10 @@
         <v>45984</v>
       </c>
       <c r="B116" t="n">
-        <v>4.389205395447081</v>
+        <v>4.382004540710095</v>
       </c>
       <c r="C116" t="n">
-        <v>4.389205395447081</v>
+        <v>4.382004540710095</v>
       </c>
     </row>
     <row r="117">
@@ -2790,10 +2790,10 @@
         <v>45985</v>
       </c>
       <c r="B117" t="n">
-        <v>4.370053551988651</v>
+        <v>4.36378815817466</v>
       </c>
       <c r="C117" t="n">
-        <v>4.370053551988651</v>
+        <v>4.36378815817466</v>
       </c>
     </row>
     <row r="118">
@@ -2812,10 +2812,10 @@
         <v>45987</v>
       </c>
       <c r="B119" t="n">
-        <v>4.441566147016368</v>
+        <v>4.44431325231302</v>
       </c>
       <c r="C119" t="n">
-        <v>4.441566147016368</v>
+        <v>4.44431325231302</v>
       </c>
     </row>
     <row r="120">
@@ -2823,10 +2823,10 @@
         <v>45988</v>
       </c>
       <c r="B120" t="n">
-        <v>4.412811588110653</v>
+        <v>4.411535791117236</v>
       </c>
       <c r="C120" t="n">
-        <v>4.412811588110653</v>
+        <v>4.411535791117236</v>
       </c>
     </row>
     <row r="121">
@@ -2834,10 +2834,10 @@
         <v>45989</v>
       </c>
       <c r="B121" t="n">
-        <v>4.400215104506776</v>
+        <v>4.406390772075257</v>
       </c>
       <c r="C121" t="n">
-        <v>4.400215104506776</v>
+        <v>4.406390772075257</v>
       </c>
     </row>
     <row r="122">
@@ -2845,10 +2845,10 @@
         <v>45990</v>
       </c>
       <c r="B122" t="n">
-        <v>4.416637825459072</v>
+        <v>4.414980388682624</v>
       </c>
       <c r="C122" t="n">
-        <v>4.416637825459072</v>
+        <v>4.414980388682624</v>
       </c>
     </row>
     <row r="123">
@@ -2856,10 +2856,10 @@
         <v>45991</v>
       </c>
       <c r="B123" t="n">
-        <v>4.427200099431129</v>
+        <v>4.425350883811149</v>
       </c>
       <c r="C123" t="n">
-        <v>4.427200099431129</v>
+        <v>4.425350883811149</v>
       </c>
     </row>
     <row r="124">
@@ -2878,10 +2878,10 @@
         <v>45993</v>
       </c>
       <c r="B125" t="n">
-        <v>4.399526876257063</v>
+        <v>4.400395908500663</v>
       </c>
       <c r="C125" t="n">
-        <v>4.399526876257063</v>
+        <v>4.400395908500663</v>
       </c>
     </row>
     <row r="126">
@@ -2889,10 +2889,10 @@
         <v>45994</v>
       </c>
       <c r="B126" t="n">
-        <v>4.440130229458708</v>
+        <v>4.439907330968061</v>
       </c>
       <c r="C126" t="n">
-        <v>4.440130229458708</v>
+        <v>4.439907330968061</v>
       </c>
     </row>
     <row r="127">
@@ -2922,10 +2922,10 @@
         <v>45997</v>
       </c>
       <c r="B129" t="n">
-        <v>4.386279414514373</v>
+        <v>4.385656366362923</v>
       </c>
       <c r="C129" t="n">
-        <v>4.386279414514373</v>
+        <v>4.385656366362923</v>
       </c>
     </row>
     <row r="130">
@@ -2955,10 +2955,10 @@
         <v>46000</v>
       </c>
       <c r="B132" t="n">
-        <v>4.371408492503349</v>
+        <v>4.371301669690899</v>
       </c>
       <c r="C132" t="n">
-        <v>4.371408492503349</v>
+        <v>4.371301669690899</v>
       </c>
     </row>
     <row r="133">
@@ -2988,10 +2988,10 @@
         <v>46003</v>
       </c>
       <c r="B135" t="n">
-        <v>4.400263111814354</v>
+        <v>4.396283881705005</v>
       </c>
       <c r="C135" t="n">
-        <v>4.400263111814354</v>
+        <v>4.396283881705005</v>
       </c>
     </row>
     <row r="136">
@@ -3010,10 +3010,10 @@
         <v>46005</v>
       </c>
       <c r="B137" t="n">
-        <v>4.425398494745943</v>
+        <v>4.421880277816443</v>
       </c>
       <c r="C137" t="n">
-        <v>4.425398494745943</v>
+        <v>4.421880277816443</v>
       </c>
     </row>
     <row r="138">
@@ -3043,10 +3043,10 @@
         <v>46008</v>
       </c>
       <c r="B140" t="n">
-        <v>4.397449118175375</v>
+        <v>4.40374985720751</v>
       </c>
       <c r="C140" t="n">
-        <v>4.397449118175375</v>
+        <v>4.40374985720751</v>
       </c>
     </row>
     <row r="141">
@@ -3054,10 +3054,10 @@
         <v>46009</v>
       </c>
       <c r="B141" t="n">
-        <v>4.384528244036699</v>
+        <v>4.381941852195989</v>
       </c>
       <c r="C141" t="n">
-        <v>4.384528244036699</v>
+        <v>4.381941852195989</v>
       </c>
     </row>
     <row r="142">
@@ -3076,10 +3076,10 @@
         <v>46011</v>
       </c>
       <c r="B143" t="n">
-        <v>4.381190211396083</v>
+        <v>4.379382563361976</v>
       </c>
       <c r="C143" t="n">
-        <v>4.381190211396083</v>
+        <v>4.379382563361976</v>
       </c>
     </row>
     <row r="144">
@@ -3087,10 +3087,10 @@
         <v>46012</v>
       </c>
       <c r="B144" t="n">
-        <v>4.300276395491455</v>
+        <v>4.29526426292682</v>
       </c>
       <c r="C144" t="n">
-        <v>4.300276395491455</v>
+        <v>4.29526426292682</v>
       </c>
     </row>
     <row r="145">
@@ -3109,10 +3109,10 @@
         <v>46014</v>
       </c>
       <c r="B146" t="n">
-        <v>4.316835394533486</v>
+        <v>4.308719154106663</v>
       </c>
       <c r="C146" t="n">
-        <v>4.316835394533486</v>
+        <v>4.308719154106663</v>
       </c>
     </row>
     <row r="147">
@@ -3145,7 +3145,7 @@
         <v>4.299888866716721</v>
       </c>
       <c r="C149" t="n">
-        <v>4.150357082514819</v>
+        <v>4.130025890217857</v>
       </c>
     </row>
     <row r="150">
@@ -3164,10 +3164,10 @@
         <v>46019</v>
       </c>
       <c r="B151" t="n">
-        <v>4.375385012024429</v>
+        <v>4.382266572176932</v>
       </c>
       <c r="C151" t="n">
-        <v>4.375385012024429</v>
+        <v>4.382266572176932</v>
       </c>
     </row>
     <row r="152">
@@ -3186,10 +3186,10 @@
         <v>46021</v>
       </c>
       <c r="B153" t="n">
-        <v>4.385414852310701</v>
+        <v>4.383737079168732</v>
       </c>
       <c r="C153" t="n">
-        <v>4.385414852310701</v>
+        <v>4.383737079168732</v>
       </c>
     </row>
     <row r="154">
@@ -3208,10 +3208,10 @@
         <v>46023</v>
       </c>
       <c r="B155" t="n">
-        <v>4.374413980625778</v>
+        <v>4.364819120896157</v>
       </c>
       <c r="C155" t="n">
-        <v>4.374413980625778</v>
+        <v>4.364819120896157</v>
       </c>
     </row>
     <row r="156">
@@ -3219,10 +3219,10 @@
         <v>46024</v>
       </c>
       <c r="B156" t="n">
-        <v>4.366378711307195</v>
+        <v>4.374115530619262</v>
       </c>
       <c r="C156" t="n">
-        <v>4.366378711307195</v>
+        <v>4.374115530619262</v>
       </c>
     </row>
     <row r="157">
@@ -3230,10 +3230,10 @@
         <v>46025</v>
       </c>
       <c r="B157" t="n">
-        <v>4.391522597901255</v>
+        <v>4.402337730452749</v>
       </c>
       <c r="C157" t="n">
-        <v>4.391522597901255</v>
+        <v>4.402337730452749</v>
       </c>
     </row>
     <row r="158">
@@ -3296,10 +3296,10 @@
         <v>46031</v>
       </c>
       <c r="B163" t="n">
-        <v>4.324648287432504</v>
+        <v>4.342046731343528</v>
       </c>
       <c r="C163" t="n">
-        <v>4.324648287432504</v>
+        <v>4.342046731343528</v>
       </c>
     </row>
     <row r="164">
@@ -3307,10 +3307,10 @@
         <v>46032</v>
       </c>
       <c r="B164" t="n">
-        <v>4.455314738873971</v>
+        <v>4.450128104267272</v>
       </c>
       <c r="C164" t="n">
-        <v>4.455314738873971</v>
+        <v>4.450128104267272</v>
       </c>
     </row>
     <row r="165">
@@ -3340,10 +3340,10 @@
         <v>46035</v>
       </c>
       <c r="B167" t="n">
-        <v>4.455547950778575</v>
+        <v>4.459585283723934</v>
       </c>
       <c r="C167" t="n">
-        <v>4.455547950778575</v>
+        <v>4.459585283723934</v>
       </c>
     </row>
     <row r="168">
@@ -3384,10 +3384,10 @@
         <v>46039</v>
       </c>
       <c r="B171" t="n">
-        <v>4.377346261759214</v>
+        <v>4.374460273552049</v>
       </c>
       <c r="C171" t="n">
-        <v>4.377346261759214</v>
+        <v>4.374460273552049</v>
       </c>
     </row>
     <row r="172">
@@ -3417,10 +3417,10 @@
         <v>46042</v>
       </c>
       <c r="B174" t="n">
-        <v>4.441663477672707</v>
+        <v>4.448140537292898</v>
       </c>
       <c r="C174" t="n">
-        <v>4.441663477672707</v>
+        <v>4.448140537292898</v>
       </c>
     </row>
     <row r="175">
@@ -3428,10 +3428,10 @@
         <v>46043</v>
       </c>
       <c r="B175" t="n">
-        <v>4.418783551765717</v>
+        <v>4.432177033977475</v>
       </c>
       <c r="C175" t="n">
-        <v>4.418783551765717</v>
+        <v>4.432177033977475</v>
       </c>
     </row>
     <row r="176">
@@ -3450,10 +3450,10 @@
         <v>46045</v>
       </c>
       <c r="B177" t="n">
-        <v>4.389639480014468</v>
+        <v>4.394347707253083</v>
       </c>
       <c r="C177" t="n">
-        <v>4.389639480014468</v>
+        <v>4.394347707253083</v>
       </c>
     </row>
     <row r="178">
@@ -3527,10 +3527,10 @@
         <v>46052</v>
       </c>
       <c r="B184" t="n">
-        <v>4.387408534405907</v>
+        <v>4.386377714971625</v>
       </c>
       <c r="C184" t="n">
-        <v>4.387408534405907</v>
+        <v>4.386377714971625</v>
       </c>
     </row>
     <row r="185">
@@ -3571,10 +3571,10 @@
         <v>46056</v>
       </c>
       <c r="B188" t="n">
-        <v>4.407068342919383</v>
+        <v>4.428205035038582</v>
       </c>
       <c r="C188" t="n">
-        <v>4.407068342919383</v>
+        <v>4.428205035038582</v>
       </c>
     </row>
     <row r="189">
@@ -3604,10 +3604,10 @@
         <v>46059</v>
       </c>
       <c r="B191" t="n">
-        <v>4.418337290791038</v>
+        <v>4.436016889007651</v>
       </c>
       <c r="C191" t="n">
-        <v>4.418337290791038</v>
+        <v>4.436016889007651</v>
       </c>
     </row>
     <row r="192">
@@ -3626,10 +3626,10 @@
         <v>46061</v>
       </c>
       <c r="B193" t="n">
-        <v>4.44954161267889</v>
+        <v>4.452837106236341</v>
       </c>
       <c r="C193" t="n">
-        <v>4.44954161267889</v>
+        <v>4.452837106236341</v>
       </c>
     </row>
     <row r="194">
@@ -3637,10 +3637,10 @@
         <v>46062</v>
       </c>
       <c r="B194" t="n">
-        <v>4.405201361250505</v>
+        <v>4.427752209515067</v>
       </c>
       <c r="C194" t="n">
-        <v>4.405201361250505</v>
+        <v>4.427752209515067</v>
       </c>
     </row>
     <row r="195">
@@ -3648,10 +3648,10 @@
         <v>46063</v>
       </c>
       <c r="B195" t="n">
-        <v>4.407812052943402</v>
+        <v>4.410437303923421</v>
       </c>
       <c r="C195" t="n">
-        <v>4.407812052943402</v>
+        <v>4.410437303923421</v>
       </c>
     </row>
     <row r="196">
@@ -3714,10 +3714,10 @@
         <v>46069</v>
       </c>
       <c r="B201" t="n">
+        <v>4.121627939830097</v>
+      </c>
+      <c r="C201" t="n">
         <v>4.045688322063411</v>
-      </c>
-      <c r="C201" t="n">
-        <v>3.99872986954666</v>
       </c>
     </row>
     <row r="202">
@@ -3725,10 +3725,10 @@
         <v>46070</v>
       </c>
       <c r="B202" t="n">
-        <v>4.146441616281752</v>
+        <v>4.153393185449035</v>
       </c>
       <c r="C202" t="n">
-        <v>4.146441616281752</v>
+        <v>4.153393185449035</v>
       </c>
     </row>
     <row r="203">
@@ -3747,10 +3747,10 @@
         <v>46072</v>
       </c>
       <c r="B204" t="n">
-        <v>4.253804257007483</v>
+        <v>4.334293454705471</v>
       </c>
       <c r="C204" t="n">
-        <v>4.253804257007483</v>
+        <v>4.334293454705471</v>
       </c>
     </row>
     <row r="205">
@@ -3780,10 +3780,10 @@
         <v>46075</v>
       </c>
       <c r="B207" t="n">
-        <v>4.43468103372181</v>
+        <v>4.442711038501733</v>
       </c>
       <c r="C207" t="n">
-        <v>4.43468103372181</v>
+        <v>4.442711038501733</v>
       </c>
     </row>
     <row r="208">
@@ -3791,10 +3791,10 @@
         <v>46076</v>
       </c>
       <c r="B208" t="n">
-        <v>4.339736405169021</v>
+        <v>4.35350279680522</v>
       </c>
       <c r="C208" t="n">
-        <v>4.339736405169021</v>
+        <v>4.35350279680522</v>
       </c>
     </row>
     <row r="209">
@@ -3813,10 +3813,10 @@
         <v>46078</v>
       </c>
       <c r="B210" t="n">
-        <v>4.3822703600396</v>
+        <v>4.39611928957235</v>
       </c>
       <c r="C210" t="n">
-        <v>4.3822703600396</v>
+        <v>4.39611928957235</v>
       </c>
     </row>
     <row r="211">
@@ -3824,10 +3824,10 @@
         <v>46079</v>
       </c>
       <c r="B211" t="n">
-        <v>4.301988969619211</v>
+        <v>4.341622069748329</v>
       </c>
       <c r="C211" t="n">
-        <v>4.301988969619211</v>
+        <v>4.341622069748329</v>
       </c>
     </row>
     <row r="212">
@@ -3835,10 +3835,10 @@
         <v>46080</v>
       </c>
       <c r="B212" t="n">
-        <v>4.380159012132893</v>
+        <v>4.389467674527096</v>
       </c>
       <c r="C212" t="n">
-        <v>4.380159012132893</v>
+        <v>4.389467674527096</v>
       </c>
     </row>
     <row r="213">
@@ -3846,10 +3846,10 @@
         <v>46081</v>
       </c>
       <c r="B213" t="n">
-        <v>4.313480972399702</v>
+        <v>4.34082739884605</v>
       </c>
       <c r="C213" t="n">
-        <v>4.313480972399702</v>
+        <v>4.34082739884605</v>
       </c>
     </row>
     <row r="214">
@@ -3879,10 +3879,10 @@
         <v>46084</v>
       </c>
       <c r="B216" t="n">
-        <v>4.361253267009833</v>
+        <v>4.416677729617398</v>
       </c>
       <c r="C216" t="n">
-        <v>4.361253267009833</v>
+        <v>4.416677729617398</v>
       </c>
     </row>
     <row r="217">
@@ -3890,10 +3890,10 @@
         <v>46085</v>
       </c>
       <c r="B217" t="n">
-        <v>4.389844452377714</v>
+        <v>4.380068376315154</v>
       </c>
       <c r="C217" t="n">
-        <v>4.389844452377714</v>
+        <v>4.380068376315154</v>
       </c>
     </row>
     <row r="218">
@@ -3923,10 +3923,10 @@
         <v>46088</v>
       </c>
       <c r="B220" t="n">
-        <v>4.486665723899269</v>
+        <v>4.484036460946214</v>
       </c>
       <c r="C220" t="n">
-        <v>4.486665723899269</v>
+        <v>4.484036460946214</v>
       </c>
     </row>
     <row r="221">
@@ -3934,10 +3934,10 @@
         <v>46089</v>
       </c>
       <c r="B221" t="n">
-        <v>4.445365984067113</v>
+        <v>4.440908423233535</v>
       </c>
       <c r="C221" t="n">
-        <v>4.445365984067113</v>
+        <v>4.440908423233535</v>
       </c>
     </row>
     <row r="222">
@@ -3945,10 +3945,10 @@
         <v>46090</v>
       </c>
       <c r="B222" t="n">
-        <v>4.453724094129533</v>
+        <v>4.470974177006687</v>
       </c>
       <c r="C222" t="n">
-        <v>4.453724094129533</v>
+        <v>4.470974177006687</v>
       </c>
     </row>
     <row r="223">
@@ -3978,10 +3978,10 @@
         <v>46093</v>
       </c>
       <c r="B225" t="n">
-        <v>4.413134920155311</v>
+        <v>4.425243241708231</v>
       </c>
       <c r="C225" t="n">
-        <v>4.413134920155311</v>
+        <v>4.425243241708231</v>
       </c>
     </row>
     <row r="226">
@@ -3989,10 +3989,10 @@
         <v>46094</v>
       </c>
       <c r="B226" t="n">
-        <v>4.380462127396035</v>
+        <v>4.433613986529599</v>
       </c>
       <c r="C226" t="n">
-        <v>4.380462127396035</v>
+        <v>4.433613986529599</v>
       </c>
     </row>
     <row r="227">
@@ -4000,10 +4000,10 @@
         <v>46095</v>
       </c>
       <c r="B227" t="n">
-        <v>4.361351984113346</v>
+        <v>4.38079408819943</v>
       </c>
       <c r="C227" t="n">
-        <v>4.361351984113346</v>
+        <v>4.38079408819943</v>
       </c>
     </row>
     <row r="228">
@@ -4011,10 +4011,10 @@
         <v>46096</v>
       </c>
       <c r="B228" t="n">
-        <v>4.27585656017375</v>
+        <v>4.300395056799331</v>
       </c>
       <c r="C228" t="n">
-        <v>4.27585656017375</v>
+        <v>4.300395056799331</v>
       </c>
     </row>
     <row r="229">
@@ -4022,10 +4022,10 @@
         <v>46097</v>
       </c>
       <c r="B229" t="n">
-        <v>4.240806226857287</v>
+        <v>4.303351536112903</v>
       </c>
       <c r="C229" t="n">
-        <v>4.240806226857287</v>
+        <v>4.303351536112903</v>
       </c>
     </row>
     <row r="230">
@@ -4044,10 +4044,10 @@
         <v>46099</v>
       </c>
       <c r="B231" t="n">
-        <v>4.437812816364118</v>
+        <v>4.452271215767234</v>
       </c>
       <c r="C231" t="n">
-        <v>4.437812816364118</v>
+        <v>4.452271215767234</v>
       </c>
     </row>
     <row r="232">
@@ -4088,7 +4088,7 @@
         <v>46103</v>
       </c>
       <c r="B235" t="n">
-        <v>3.829216383692828</v>
+        <v>3.873733478391508</v>
       </c>
       <c r="C235" t="n">
         <v>4.137866466721963</v>
@@ -4110,10 +4110,10 @@
         <v>46105</v>
       </c>
       <c r="B237" t="n">
-        <v>4.255727061512628</v>
+        <v>4.278635411236909</v>
       </c>
       <c r="C237" t="n">
-        <v>4.300941620347608</v>
+        <v>4.323849970071889</v>
       </c>
     </row>
     <row r="238">
@@ -4121,10 +4121,10 @@
         <v>46106</v>
       </c>
       <c r="B238" t="n">
-        <v>4.288328682649125</v>
+        <v>4.290056004910739</v>
       </c>
       <c r="C238" t="n">
-        <v>4.288328682649125</v>
+        <v>4.290056004910739</v>
       </c>
     </row>
     <row r="239">
@@ -4132,10 +4132,10 @@
         <v>46107</v>
       </c>
       <c r="B239" t="n">
-        <v>4.339900450666143</v>
+        <v>4.3508651752634</v>
       </c>
       <c r="C239" t="n">
-        <v>4.339900450666143</v>
+        <v>4.3508651752634</v>
       </c>
     </row>
     <row r="240">
@@ -4143,10 +4143,10 @@
         <v>46108</v>
       </c>
       <c r="B240" t="n">
-        <v>4.375269176703401</v>
+        <v>4.376940015975062</v>
       </c>
       <c r="C240" t="n">
-        <v>4.375269176703401</v>
+        <v>4.376940015975062</v>
       </c>
     </row>
     <row r="241">
@@ -4154,10 +4154,10 @@
         <v>46109</v>
       </c>
       <c r="B241" t="n">
-        <v>4.400371626682975</v>
+        <v>4.381993551924698</v>
       </c>
       <c r="C241" t="n">
-        <v>4.400371626682975</v>
+        <v>4.381993551924698</v>
       </c>
     </row>
     <row r="242">
@@ -4176,10 +4176,10 @@
         <v>46111</v>
       </c>
       <c r="B243" t="n">
-        <v>4.381824287198912</v>
+        <v>4.392778137416178</v>
       </c>
       <c r="C243" t="n">
-        <v>4.381824287198912</v>
+        <v>4.392778137416178</v>
       </c>
     </row>
     <row r="244">
@@ -4187,10 +4187,10 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>4.399987097672689</v>
+        <v>4.418222806960536</v>
       </c>
       <c r="C244" t="n">
-        <v>4.399987097672689</v>
+        <v>4.418222806960536</v>
       </c>
     </row>
     <row r="245">
@@ -4209,10 +4209,10 @@
         <v>46114</v>
       </c>
       <c r="B246" t="n">
-        <v>4.406015159075779</v>
+        <v>4.404306582918148</v>
       </c>
       <c r="C246" t="n">
-        <v>4.406015159075779</v>
+        <v>4.404306582918148</v>
       </c>
     </row>
     <row r="247">
@@ -4220,10 +4220,10 @@
         <v>46115</v>
       </c>
       <c r="B247" t="n">
-        <v>4.430568963901477</v>
+        <v>4.473288173718211</v>
       </c>
       <c r="C247" t="n">
-        <v>4.430568963901477</v>
+        <v>4.473288173718211</v>
       </c>
     </row>
     <row r="248">
@@ -4242,10 +4242,10 @@
         <v>46117</v>
       </c>
       <c r="B249" t="n">
-        <v>4.321276747079891</v>
+        <v>4.350509940186857</v>
       </c>
       <c r="C249" t="n">
-        <v>4.321276747079891</v>
+        <v>4.350509940186857</v>
       </c>
     </row>
     <row r="250">
@@ -4253,10 +4253,10 @@
         <v>46118</v>
       </c>
       <c r="B250" t="n">
-        <v>4.367961969537408</v>
+        <v>4.405849718984344</v>
       </c>
       <c r="C250" t="n">
-        <v>4.367961969537408</v>
+        <v>4.405849718984344</v>
       </c>
     </row>
     <row r="251">
@@ -4264,10 +4264,10 @@
         <v>46119</v>
       </c>
       <c r="B251" t="n">
-        <v>4.394948134322497</v>
+        <v>4.390438825748557</v>
       </c>
       <c r="C251" t="n">
-        <v>4.394948134322497</v>
+        <v>4.390438825748557</v>
       </c>
     </row>
     <row r="252">
@@ -4275,10 +4275,10 @@
         <v>46120</v>
       </c>
       <c r="B252" t="n">
-        <v>4.339321391075468</v>
+        <v>4.365099911205885</v>
       </c>
       <c r="C252" t="n">
-        <v>4.339321391075468</v>
+        <v>4.365099911205885</v>
       </c>
     </row>
     <row r="253">
@@ -4308,7 +4308,7 @@
         <v>46123</v>
       </c>
       <c r="B255" t="n">
-        <v>4.391381372384599</v>
+        <v>4.397923819150005</v>
       </c>
       <c r="C255" t="n">
         <v>4.381300735889687</v>
@@ -4319,7 +4319,7 @@
         <v>46124</v>
       </c>
       <c r="B256" t="n">
-        <v>4.411435329640704</v>
+        <v>4.400017698377419</v>
       </c>
       <c r="C256" t="n">
         <v>4.301666949172199</v>
@@ -4330,10 +4330,10 @@
         <v>46125</v>
       </c>
       <c r="B257" t="n">
-        <v>4.398262356472682</v>
+        <v>4.358362233483422</v>
       </c>
       <c r="C257" t="n">
-        <v>4.358362233483422</v>
+        <v>4.301860686916426</v>
       </c>
     </row>
   </sheetData>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1877290305792663</v>
+        <v>-0.185604444044781</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09307032545313376</v>
+        <v>0.06717381619772089</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4104659992706736</v>
+        <v>-0.4276904481164854</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1031848837166507</v>
+        <v>-0.08331153299341088</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1344820930893578</v>
+        <v>-0.1381848324572648</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4639505789299041</v>
+        <v>0.4122018269289778</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4251598060668353</v>
+        <v>0.3964719522551898</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6010,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5595534567218676</v>
+        <v>0.5177403446850004</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5686849621369348</v>
+        <v>0.5608972395393494</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -6151,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.191135583662712</v>
+        <v>0.145256077129281</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
